--- a/Score_Class_2026.xlsx
+++ b/Score_Class_2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phisan\Consultancy\2569-KU_MapProjection\Admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F95260-3310-4AD7-9563-9FBF5D5245AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0E30FD-9ACC-4D43-81EE-8E4566F2BCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38300" yWindow="-7000" windowWidth="18380" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="39620" yWindow="-7000" windowWidth="18090" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exercise" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="494" uniqueCount="312">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="315">
   <si>
     <t>รายงานแสดงจำนวนนิสิต จำแนกตามหมู่เรียน ภาคต้น ปีการศึกษา 2569</t>
   </si>
@@ -970,6 +970,15 @@
   </si>
   <si>
     <t>Ex.8 Planar Map Projection</t>
+  </si>
+  <si>
+    <t>21/Sept/2569</t>
+  </si>
+  <si>
+    <t>Ex.9 Mercator vs EqualEarth</t>
+  </si>
+  <si>
+    <t>Ex. UTM zone 47/48</t>
   </si>
 </sst>
 </file>
@@ -979,7 +988,7 @@
   <numFmts count="1">
     <numFmt numFmtId="187" formatCode="B1d\-mmm\-yy"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -1040,6 +1049,12 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -1051,12 +1066,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1075,6 +1084,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1119,7 +1134,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1172,52 +1187,54 @@
     <xf numFmtId="187" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="187" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="187" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1256,7 +1273,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>1313180</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>1423330</xdr:rowOff>
+      <xdr:rowOff>1420790</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1452,54 +1469,55 @@
     <col min="7" max="8" width="10" hidden="1" customWidth="1"/>
     <col min="9" max="11" width="10.796875" hidden="1" customWidth="1"/>
     <col min="12" max="20" width="4.6484375" style="8" customWidth="1"/>
-    <col min="21" max="26" width="4.796875" customWidth="1"/>
+    <col min="21" max="21" width="4.796875" style="8" customWidth="1"/>
+    <col min="22" max="26" width="4.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:26" ht="16" customHeight="1">
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="38"/>
-      <c r="D2" s="38"/>
-      <c r="E2" s="38"/>
-      <c r="F2" s="38"/>
-      <c r="G2" s="38"/>
-      <c r="H2" s="38"/>
-      <c r="I2" s="38"/>
-      <c r="J2" s="38"/>
-      <c r="K2" s="38"/>
-      <c r="L2" s="38"/>
-      <c r="M2" s="38"/>
-      <c r="N2" s="38"/>
-      <c r="O2" s="38"/>
-      <c r="P2" s="38"/>
-      <c r="Q2" s="38"/>
-      <c r="R2" s="38"/>
-      <c r="S2" s="38"/>
-      <c r="T2" s="38"/>
+      <c r="C2" s="40"/>
+      <c r="D2" s="40"/>
+      <c r="E2" s="40"/>
+      <c r="F2" s="40"/>
+      <c r="G2" s="40"/>
+      <c r="H2" s="40"/>
+      <c r="I2" s="40"/>
+      <c r="J2" s="40"/>
+      <c r="K2" s="40"/>
+      <c r="L2" s="40"/>
+      <c r="M2" s="40"/>
+      <c r="N2" s="40"/>
+      <c r="O2" s="40"/>
+      <c r="P2" s="40"/>
+      <c r="Q2" s="40"/>
+      <c r="R2" s="40"/>
+      <c r="S2" s="40"/>
+      <c r="T2" s="40"/>
     </row>
     <row r="3" spans="2:26" ht="18.3" customHeight="1">
-      <c r="B3" s="38" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="38"/>
-      <c r="G3" s="38"/>
-      <c r="H3" s="38"/>
-      <c r="I3" s="38"/>
-      <c r="J3" s="38"/>
-      <c r="K3" s="38"/>
-      <c r="L3" s="38"/>
-      <c r="M3" s="38"/>
-      <c r="N3" s="38"/>
-      <c r="O3" s="38"/>
-      <c r="P3" s="38"/>
-      <c r="Q3" s="38"/>
-      <c r="R3" s="38"/>
-      <c r="S3" s="38"/>
-      <c r="T3" s="38"/>
+      <c r="B3" s="40" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="40"/>
+      <c r="D3" s="40"/>
+      <c r="E3" s="40"/>
+      <c r="F3" s="40"/>
+      <c r="G3" s="40"/>
+      <c r="H3" s="40"/>
+      <c r="I3" s="40"/>
+      <c r="J3" s="40"/>
+      <c r="K3" s="40"/>
+      <c r="L3" s="40"/>
+      <c r="M3" s="40"/>
+      <c r="N3" s="40"/>
+      <c r="O3" s="40"/>
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
     </row>
     <row r="4" spans="2:26" ht="26.1" customHeight="1">
       <c r="B4" s="1" t="s">
@@ -1508,16 +1526,16 @@
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="39" t="s">
+      <c r="M4" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="39"/>
-      <c r="O4" s="39"/>
-      <c r="P4" s="39"/>
-      <c r="Q4" s="39"/>
-      <c r="R4" s="39"/>
-      <c r="S4" s="39"/>
-      <c r="T4" s="39"/>
+      <c r="N4" s="41"/>
+      <c r="O4" s="41"/>
+      <c r="P4" s="41"/>
+      <c r="Q4" s="41"/>
+      <c r="R4" s="41"/>
+      <c r="S4" s="41"/>
+      <c r="T4" s="41"/>
     </row>
     <row r="5" spans="2:26" ht="18">
       <c r="E5" s="1" t="s">
@@ -1543,7 +1561,7 @@
       <c r="M6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="28" t="s">
+      <c r="N6" s="25" t="s">
         <v>12</v>
       </c>
       <c r="O6" s="11" t="s">
@@ -1552,7 +1570,7 @@
       <c r="P6" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="Q6" s="29" t="s">
+      <c r="Q6" s="26" t="s">
         <v>308</v>
       </c>
       <c r="R6" s="11" t="s">
@@ -1561,8 +1579,12 @@
       <c r="S6" s="11" t="s">
         <v>311</v>
       </c>
-      <c r="T6" s="10"/>
-      <c r="U6" s="9"/>
+      <c r="T6" s="11" t="s">
+        <v>313</v>
+      </c>
+      <c r="U6" s="11" t="s">
+        <v>314</v>
+      </c>
       <c r="V6" s="9"/>
       <c r="W6" s="9"/>
       <c r="X6" s="9"/>
@@ -1600,32 +1622,36 @@
       <c r="K7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="22">
+      <c r="L7" s="20">
         <v>12</v>
       </c>
-      <c r="M7" s="22">
-        <v>10</v>
-      </c>
-      <c r="N7" s="22">
-        <v>10</v>
-      </c>
-      <c r="O7" s="22">
-        <v>10</v>
-      </c>
-      <c r="P7" s="22">
-        <v>10</v>
-      </c>
-      <c r="Q7" s="30">
+      <c r="M7" s="20">
+        <v>10</v>
+      </c>
+      <c r="N7" s="20">
+        <v>10</v>
+      </c>
+      <c r="O7" s="20">
+        <v>10</v>
+      </c>
+      <c r="P7" s="20">
+        <v>10</v>
+      </c>
+      <c r="Q7" s="27">
         <v>26</v>
       </c>
-      <c r="R7" s="22">
-        <v>10</v>
-      </c>
-      <c r="S7" s="22">
-        <v>10</v>
-      </c>
-      <c r="T7" s="22"/>
-      <c r="U7" s="9"/>
+      <c r="R7" s="20">
+        <v>10</v>
+      </c>
+      <c r="S7" s="20">
+        <v>10</v>
+      </c>
+      <c r="T7" s="20">
+        <v>10</v>
+      </c>
+      <c r="U7" s="20">
+        <v>10</v>
+      </c>
       <c r="V7" s="9"/>
       <c r="W7" s="9"/>
       <c r="X7" s="9"/>
@@ -1672,17 +1698,19 @@
       <c r="P8" s="10">
         <v>8</v>
       </c>
-      <c r="Q8" s="31">
+      <c r="Q8" s="28">
         <v>10</v>
       </c>
       <c r="R8" s="10">
         <v>5</v>
       </c>
-      <c r="S8" s="10">
-        <v>0</v>
-      </c>
-      <c r="T8" s="10"/>
-      <c r="U8" s="9"/>
+      <c r="S8" s="10"/>
+      <c r="T8" s="10">
+        <v>7</v>
+      </c>
+      <c r="U8" s="10">
+        <v>9</v>
+      </c>
       <c r="V8" s="9"/>
       <c r="W8" s="9"/>
       <c r="X8" s="9"/>
@@ -1729,7 +1757,7 @@
         <v>10</v>
       </c>
       <c r="P9" s="10"/>
-      <c r="Q9" s="31">
+      <c r="Q9" s="28">
         <v>4</v>
       </c>
       <c r="R9" s="10">
@@ -1738,8 +1766,12 @@
       <c r="S9" s="10">
         <v>10</v>
       </c>
-      <c r="T9" s="10"/>
-      <c r="U9" s="9"/>
+      <c r="T9" s="10">
+        <v>7</v>
+      </c>
+      <c r="U9" s="10">
+        <v>9</v>
+      </c>
       <c r="V9" s="9"/>
       <c r="W9" s="9"/>
       <c r="X9" s="9"/>
@@ -1788,15 +1820,19 @@
       <c r="P10" s="10">
         <v>8</v>
       </c>
-      <c r="Q10" s="31">
+      <c r="Q10" s="28">
         <v>4</v>
       </c>
       <c r="R10" s="10"/>
       <c r="S10" s="10">
         <v>10</v>
       </c>
-      <c r="T10" s="10"/>
-      <c r="U10" s="9"/>
+      <c r="T10" s="10">
+        <v>10</v>
+      </c>
+      <c r="U10" s="10">
+        <v>10</v>
+      </c>
       <c r="V10" s="9"/>
       <c r="W10" s="9"/>
       <c r="X10" s="9"/>
@@ -1849,7 +1885,7 @@
       <c r="P11" s="10">
         <v>9</v>
       </c>
-      <c r="Q11" s="31">
+      <c r="Q11" s="28">
         <v>9</v>
       </c>
       <c r="R11" s="10">
@@ -1858,8 +1894,12 @@
       <c r="S11" s="10">
         <v>10</v>
       </c>
-      <c r="T11" s="10"/>
-      <c r="U11" s="9"/>
+      <c r="T11" s="10">
+        <v>7</v>
+      </c>
+      <c r="U11" s="10">
+        <v>7</v>
+      </c>
       <c r="V11" s="9"/>
       <c r="W11" s="9"/>
       <c r="X11" s="9"/>
@@ -1906,7 +1946,7 @@
       <c r="P12" s="10">
         <v>10</v>
       </c>
-      <c r="Q12" s="31">
+      <c r="Q12" s="28">
         <v>9</v>
       </c>
       <c r="R12" s="10">
@@ -1915,8 +1955,12 @@
       <c r="S12" s="10">
         <v>10</v>
       </c>
-      <c r="T12" s="10"/>
-      <c r="U12" s="9"/>
+      <c r="T12" s="10">
+        <v>7</v>
+      </c>
+      <c r="U12" s="10">
+        <v>8</v>
+      </c>
       <c r="V12" s="9"/>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
@@ -1959,7 +2003,7 @@
       <c r="N13" s="10"/>
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
-      <c r="Q13" s="31">
+      <c r="Q13" s="28">
         <v>0</v>
       </c>
       <c r="R13" s="10">
@@ -1968,8 +2012,12 @@
       <c r="S13" s="10">
         <v>10</v>
       </c>
-      <c r="T13" s="10"/>
-      <c r="U13" s="9"/>
+      <c r="T13" s="10">
+        <v>5</v>
+      </c>
+      <c r="U13" s="10">
+        <v>9</v>
+      </c>
       <c r="V13" s="9"/>
       <c r="W13" s="9"/>
       <c r="X13" s="9"/>
@@ -2018,7 +2066,7 @@
       <c r="P14" s="10">
         <v>8</v>
       </c>
-      <c r="Q14" s="31">
+      <c r="Q14" s="28">
         <v>2</v>
       </c>
       <c r="R14" s="10">
@@ -2027,8 +2075,12 @@
       <c r="S14" s="10">
         <v>3</v>
       </c>
-      <c r="T14" s="10"/>
-      <c r="U14" s="9"/>
+      <c r="T14" s="10">
+        <v>7</v>
+      </c>
+      <c r="U14" s="10">
+        <v>7</v>
+      </c>
       <c r="V14" s="9"/>
       <c r="W14" s="9"/>
       <c r="X14" s="9"/>
@@ -2081,7 +2133,7 @@
       <c r="P15" s="10">
         <v>8</v>
       </c>
-      <c r="Q15" s="31">
+      <c r="Q15" s="28">
         <v>11</v>
       </c>
       <c r="R15" s="10">
@@ -2090,8 +2142,12 @@
       <c r="S15" s="10">
         <v>8</v>
       </c>
-      <c r="T15" s="10"/>
-      <c r="U15" s="9"/>
+      <c r="T15" s="10">
+        <v>6</v>
+      </c>
+      <c r="U15" s="10">
+        <v>7</v>
+      </c>
       <c r="V15" s="9"/>
       <c r="W15" s="9"/>
       <c r="X15" s="9"/>
@@ -2140,7 +2196,7 @@
         <v>5</v>
       </c>
       <c r="P16" s="10"/>
-      <c r="Q16" s="31">
+      <c r="Q16" s="28">
         <v>14</v>
       </c>
       <c r="R16" s="10">
@@ -2149,8 +2205,12 @@
       <c r="S16" s="10">
         <v>10</v>
       </c>
-      <c r="T16" s="10"/>
-      <c r="U16" s="9"/>
+      <c r="T16" s="10">
+        <v>7</v>
+      </c>
+      <c r="U16" s="10">
+        <v>6</v>
+      </c>
       <c r="V16" s="9"/>
       <c r="W16" s="9"/>
       <c r="X16" s="9"/>
@@ -2203,7 +2263,7 @@
       <c r="P17" s="10">
         <v>10</v>
       </c>
-      <c r="Q17" s="31">
+      <c r="Q17" s="28">
         <v>9</v>
       </c>
       <c r="R17" s="10">
@@ -2212,8 +2272,12 @@
       <c r="S17" s="10">
         <v>10</v>
       </c>
-      <c r="T17" s="10"/>
-      <c r="U17" s="9"/>
+      <c r="T17" s="10">
+        <v>7</v>
+      </c>
+      <c r="U17" s="10">
+        <v>6</v>
+      </c>
       <c r="V17" s="9"/>
       <c r="W17" s="9"/>
       <c r="X17" s="9"/>
@@ -2262,7 +2326,7 @@
       <c r="P18" s="10">
         <v>9</v>
       </c>
-      <c r="Q18" s="31">
+      <c r="Q18" s="28">
         <v>2</v>
       </c>
       <c r="R18" s="10">
@@ -2271,8 +2335,12 @@
       <c r="S18" s="10">
         <v>10</v>
       </c>
-      <c r="T18" s="10"/>
-      <c r="U18" s="9"/>
+      <c r="T18" s="10">
+        <v>6</v>
+      </c>
+      <c r="U18" s="10">
+        <v>10</v>
+      </c>
       <c r="V18" s="9"/>
       <c r="W18" s="9"/>
       <c r="X18" s="9"/>
@@ -2315,7 +2383,7 @@
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
-      <c r="Q19" s="31">
+      <c r="Q19" s="28">
         <v>0</v>
       </c>
       <c r="R19" s="10">
@@ -2324,8 +2392,12 @@
       <c r="S19" s="10">
         <v>10</v>
       </c>
-      <c r="T19" s="10"/>
-      <c r="U19" s="9"/>
+      <c r="T19" s="10">
+        <v>7</v>
+      </c>
+      <c r="U19" s="10">
+        <v>7</v>
+      </c>
       <c r="V19" s="9"/>
       <c r="W19" s="9"/>
       <c r="X19" s="9"/>
@@ -2378,15 +2450,19 @@
       <c r="P20" s="10">
         <v>10</v>
       </c>
-      <c r="Q20" s="31">
+      <c r="Q20" s="28">
         <v>5</v>
       </c>
       <c r="R20" s="10">
         <v>5</v>
       </c>
       <c r="S20" s="10"/>
-      <c r="T20" s="10"/>
-      <c r="U20" s="9"/>
+      <c r="T20" s="10">
+        <v>7</v>
+      </c>
+      <c r="U20" s="10">
+        <v>7</v>
+      </c>
       <c r="V20" s="9"/>
       <c r="W20" s="9"/>
       <c r="X20" s="9"/>
@@ -2435,15 +2511,19 @@
         <v>5</v>
       </c>
       <c r="P21" s="10"/>
-      <c r="Q21" s="31">
+      <c r="Q21" s="28">
         <v>6</v>
       </c>
       <c r="R21" s="10"/>
       <c r="S21" s="10">
         <v>10</v>
       </c>
-      <c r="T21" s="10"/>
-      <c r="U21" s="9"/>
+      <c r="T21" s="10">
+        <v>8</v>
+      </c>
+      <c r="U21" s="10">
+        <v>8</v>
+      </c>
       <c r="V21" s="9"/>
       <c r="W21" s="9"/>
       <c r="X21" s="9"/>
@@ -2496,7 +2576,7 @@
       <c r="P22" s="10">
         <v>10</v>
       </c>
-      <c r="Q22" s="31">
+      <c r="Q22" s="28">
         <v>2</v>
       </c>
       <c r="R22" s="10">
@@ -2506,7 +2586,7 @@
         <v>9</v>
       </c>
       <c r="T22" s="10"/>
-      <c r="U22" s="9"/>
+      <c r="U22" s="10"/>
       <c r="V22" s="9"/>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
@@ -2559,7 +2639,7 @@
       <c r="P23" s="10">
         <v>10</v>
       </c>
-      <c r="Q23" s="31">
+      <c r="Q23" s="28">
         <v>16</v>
       </c>
       <c r="R23" s="10">
@@ -2568,8 +2648,12 @@
       <c r="S23" s="10">
         <v>10</v>
       </c>
-      <c r="T23" s="10"/>
-      <c r="U23" s="9"/>
+      <c r="T23" s="10">
+        <v>10</v>
+      </c>
+      <c r="U23" s="10">
+        <v>10</v>
+      </c>
       <c r="V23" s="9"/>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
@@ -2622,7 +2706,7 @@
       <c r="P24" s="10">
         <v>10</v>
       </c>
-      <c r="Q24" s="31">
+      <c r="Q24" s="28">
         <v>12</v>
       </c>
       <c r="R24" s="10">
@@ -2631,8 +2715,12 @@
       <c r="S24" s="10">
         <v>10</v>
       </c>
-      <c r="T24" s="10"/>
-      <c r="U24" s="9"/>
+      <c r="T24" s="10">
+        <v>10</v>
+      </c>
+      <c r="U24" s="10">
+        <v>10</v>
+      </c>
       <c r="V24" s="9"/>
       <c r="W24" s="9"/>
       <c r="X24" s="9"/>
@@ -2685,7 +2773,7 @@
       <c r="P25" s="10">
         <v>10</v>
       </c>
-      <c r="Q25" s="31">
+      <c r="Q25" s="28">
         <v>9</v>
       </c>
       <c r="R25" s="10">
@@ -2694,8 +2782,12 @@
       <c r="S25" s="10">
         <v>5</v>
       </c>
-      <c r="T25" s="10"/>
-      <c r="U25" s="9"/>
+      <c r="T25" s="10">
+        <v>7</v>
+      </c>
+      <c r="U25" s="10">
+        <v>8</v>
+      </c>
       <c r="V25" s="9"/>
       <c r="W25" s="9"/>
       <c r="X25" s="9"/>
@@ -2748,7 +2840,7 @@
       <c r="P26" s="10">
         <v>10</v>
       </c>
-      <c r="Q26" s="31">
+      <c r="Q26" s="28">
         <v>1</v>
       </c>
       <c r="R26" s="10">
@@ -2757,8 +2849,12 @@
       <c r="S26" s="10">
         <v>10</v>
       </c>
-      <c r="T26" s="10"/>
-      <c r="U26" s="9"/>
+      <c r="T26" s="10">
+        <v>8</v>
+      </c>
+      <c r="U26" s="10">
+        <v>8</v>
+      </c>
       <c r="V26" s="9"/>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
@@ -2809,7 +2905,7 @@
       <c r="P27" s="10">
         <v>10</v>
       </c>
-      <c r="Q27" s="31">
+      <c r="Q27" s="28">
         <v>1</v>
       </c>
       <c r="R27" s="10">
@@ -2818,8 +2914,12 @@
       <c r="S27" s="10">
         <v>10</v>
       </c>
-      <c r="T27" s="10"/>
-      <c r="U27" s="9"/>
+      <c r="T27" s="10">
+        <v>8</v>
+      </c>
+      <c r="U27" s="10">
+        <v>10</v>
+      </c>
       <c r="V27" s="9"/>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
@@ -2868,7 +2968,7 @@
         <v>4</v>
       </c>
       <c r="P28" s="10"/>
-      <c r="Q28" s="31">
+      <c r="Q28" s="28">
         <v>8</v>
       </c>
       <c r="R28" s="10">
@@ -2878,7 +2978,7 @@
         <v>10</v>
       </c>
       <c r="T28" s="10"/>
-      <c r="U28" s="9"/>
+      <c r="U28" s="10"/>
       <c r="V28" s="9"/>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
@@ -2931,7 +3031,7 @@
       <c r="P29" s="10">
         <v>10</v>
       </c>
-      <c r="Q29" s="31">
+      <c r="Q29" s="28">
         <v>9</v>
       </c>
       <c r="R29" s="10">
@@ -2940,8 +3040,12 @@
       <c r="S29" s="10">
         <v>10</v>
       </c>
-      <c r="T29" s="10"/>
-      <c r="U29" s="9"/>
+      <c r="T29" s="10">
+        <v>10</v>
+      </c>
+      <c r="U29" s="10">
+        <v>10</v>
+      </c>
       <c r="V29" s="9"/>
       <c r="W29" s="9"/>
       <c r="X29" s="9"/>
@@ -2994,7 +3098,7 @@
       <c r="P30" s="10">
         <v>10</v>
       </c>
-      <c r="Q30" s="31">
+      <c r="Q30" s="28">
         <v>11</v>
       </c>
       <c r="R30" s="10">
@@ -3003,8 +3107,12 @@
       <c r="S30" s="10">
         <v>10</v>
       </c>
-      <c r="T30" s="10"/>
-      <c r="U30" s="9"/>
+      <c r="T30" s="10">
+        <v>8</v>
+      </c>
+      <c r="U30" s="10">
+        <v>10</v>
+      </c>
       <c r="V30" s="9"/>
       <c r="W30" s="9"/>
       <c r="X30" s="9"/>
@@ -3012,51 +3120,51 @@
       <c r="Z30" s="9"/>
     </row>
     <row r="31" spans="2:26" ht="18">
-      <c r="B31" s="32" t="s">
+      <c r="B31" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="C31" s="33" t="s">
+      <c r="C31" s="30" t="s">
         <v>165</v>
       </c>
-      <c r="D31" s="33" t="s">
+      <c r="D31" s="30" t="s">
         <v>166</v>
       </c>
-      <c r="E31" s="33" t="s">
+      <c r="E31" s="30" t="s">
         <v>167</v>
       </c>
-      <c r="F31" s="33" t="s">
+      <c r="F31" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="G31" s="33" t="s">
+      <c r="G31" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="H31" s="33" t="s">
+      <c r="H31" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="I31" s="33" t="s">
+      <c r="I31" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="J31" s="33" t="s">
+      <c r="J31" s="30" t="s">
         <v>168</v>
       </c>
-      <c r="K31" s="34" t="s">
+      <c r="K31" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="L31" s="35"/>
-      <c r="M31" s="35"/>
-      <c r="N31" s="35"/>
-      <c r="O31" s="35"/>
-      <c r="P31" s="35"/>
-      <c r="Q31" s="35"/>
-      <c r="R31" s="35"/>
-      <c r="S31" s="35"/>
-      <c r="T31" s="35"/>
-      <c r="U31" s="36"/>
-      <c r="V31" s="36"/>
-      <c r="W31" s="36"/>
-      <c r="X31" s="36"/>
-      <c r="Y31" s="36"/>
-      <c r="Z31" s="36"/>
+      <c r="L31" s="32"/>
+      <c r="M31" s="32"/>
+      <c r="N31" s="32"/>
+      <c r="O31" s="32"/>
+      <c r="P31" s="32"/>
+      <c r="Q31" s="32"/>
+      <c r="R31" s="32"/>
+      <c r="S31" s="32"/>
+      <c r="T31" s="32"/>
+      <c r="U31" s="32"/>
+      <c r="V31" s="33"/>
+      <c r="W31" s="33"/>
+      <c r="X31" s="33"/>
+      <c r="Y31" s="33"/>
+      <c r="Z31" s="33"/>
     </row>
     <row r="32" spans="2:26" ht="18">
       <c r="B32" s="5" t="s">
@@ -3104,7 +3212,7 @@
       <c r="P32" s="10">
         <v>10</v>
       </c>
-      <c r="Q32" s="31">
+      <c r="Q32" s="28">
         <v>14</v>
       </c>
       <c r="R32" s="10">
@@ -3113,8 +3221,12 @@
       <c r="S32" s="10">
         <v>10</v>
       </c>
-      <c r="T32" s="10"/>
-      <c r="U32" s="9"/>
+      <c r="T32" s="10">
+        <v>7</v>
+      </c>
+      <c r="U32" s="10">
+        <v>7</v>
+      </c>
       <c r="V32" s="9"/>
       <c r="W32" s="9"/>
       <c r="X32" s="9"/>
@@ -3165,7 +3277,7 @@
       <c r="P33" s="10">
         <v>10</v>
       </c>
-      <c r="Q33" s="31">
+      <c r="Q33" s="28">
         <v>3</v>
       </c>
       <c r="R33" s="10">
@@ -3175,7 +3287,9 @@
         <v>10</v>
       </c>
       <c r="T33" s="10"/>
-      <c r="U33" s="9"/>
+      <c r="U33" s="10">
+        <v>10</v>
+      </c>
       <c r="V33" s="9"/>
       <c r="W33" s="9"/>
       <c r="X33" s="9"/>
@@ -3237,8 +3351,12 @@
       <c r="S34" s="10">
         <v>10</v>
       </c>
-      <c r="T34" s="10"/>
-      <c r="U34" s="9"/>
+      <c r="T34" s="10">
+        <v>7</v>
+      </c>
+      <c r="U34" s="10">
+        <v>10</v>
+      </c>
       <c r="V34" s="9"/>
       <c r="W34" s="9"/>
       <c r="X34" s="9"/>
@@ -3291,7 +3409,7 @@
       <c r="P35" s="10">
         <v>10</v>
       </c>
-      <c r="Q35" s="31">
+      <c r="Q35" s="28">
         <v>17</v>
       </c>
       <c r="R35" s="10">
@@ -3300,8 +3418,12 @@
       <c r="S35" s="10">
         <v>10</v>
       </c>
-      <c r="T35" s="10"/>
-      <c r="U35" s="9"/>
+      <c r="T35" s="10">
+        <v>7</v>
+      </c>
+      <c r="U35" s="10">
+        <v>9</v>
+      </c>
       <c r="V35" s="9"/>
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
@@ -3354,7 +3476,7 @@
       <c r="P36" s="10">
         <v>10</v>
       </c>
-      <c r="Q36" s="31">
+      <c r="Q36" s="28">
         <v>7</v>
       </c>
       <c r="R36" s="10">
@@ -3363,8 +3485,12 @@
       <c r="S36" s="10">
         <v>10</v>
       </c>
-      <c r="T36" s="10"/>
-      <c r="U36" s="9"/>
+      <c r="T36" s="10">
+        <v>7</v>
+      </c>
+      <c r="U36" s="10">
+        <v>7</v>
+      </c>
       <c r="V36" s="9"/>
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
@@ -3417,7 +3543,7 @@
       <c r="P37" s="10">
         <v>9</v>
       </c>
-      <c r="Q37" s="31">
+      <c r="Q37" s="28">
         <v>17</v>
       </c>
       <c r="R37" s="10">
@@ -3426,8 +3552,12 @@
       <c r="S37" s="10">
         <v>10</v>
       </c>
-      <c r="T37" s="10"/>
-      <c r="U37" s="9"/>
+      <c r="T37" s="10">
+        <v>7</v>
+      </c>
+      <c r="U37" s="10">
+        <v>6</v>
+      </c>
       <c r="V37" s="9"/>
       <c r="W37" s="9"/>
       <c r="X37" s="9"/>
@@ -3478,7 +3608,7 @@
       <c r="P38" s="10">
         <v>10</v>
       </c>
-      <c r="Q38" s="31">
+      <c r="Q38" s="28">
         <v>16</v>
       </c>
       <c r="R38" s="10">
@@ -3487,8 +3617,12 @@
       <c r="S38" s="10">
         <v>10</v>
       </c>
-      <c r="T38" s="10"/>
-      <c r="U38" s="9"/>
+      <c r="T38" s="10">
+        <v>7</v>
+      </c>
+      <c r="U38" s="10">
+        <v>8</v>
+      </c>
       <c r="V38" s="9"/>
       <c r="W38" s="9"/>
       <c r="X38" s="9"/>
@@ -3541,7 +3675,7 @@
       <c r="P39" s="10">
         <v>10</v>
       </c>
-      <c r="Q39" s="31">
+      <c r="Q39" s="28">
         <v>22</v>
       </c>
       <c r="R39" s="10">
@@ -3550,8 +3684,12 @@
       <c r="S39" s="10">
         <v>10</v>
       </c>
-      <c r="T39" s="10"/>
-      <c r="U39" s="9"/>
+      <c r="T39" s="10">
+        <v>10</v>
+      </c>
+      <c r="U39" s="10">
+        <v>10</v>
+      </c>
       <c r="V39" s="9"/>
       <c r="W39" s="9"/>
       <c r="X39" s="9"/>
@@ -3604,7 +3742,7 @@
       <c r="P40" s="10">
         <v>10</v>
       </c>
-      <c r="Q40" s="31">
+      <c r="Q40" s="28">
         <v>15</v>
       </c>
       <c r="R40" s="10">
@@ -3613,8 +3751,12 @@
       <c r="S40" s="10">
         <v>10</v>
       </c>
-      <c r="T40" s="10"/>
-      <c r="U40" s="9"/>
+      <c r="T40" s="10">
+        <v>7</v>
+      </c>
+      <c r="U40" s="10">
+        <v>10</v>
+      </c>
       <c r="V40" s="9"/>
       <c r="W40" s="9"/>
       <c r="X40" s="9"/>
@@ -3667,7 +3809,7 @@
       <c r="P41" s="10">
         <v>10</v>
       </c>
-      <c r="Q41" s="31">
+      <c r="Q41" s="28">
         <v>6</v>
       </c>
       <c r="R41" s="10">
@@ -3676,8 +3818,12 @@
       <c r="S41" s="10">
         <v>10</v>
       </c>
-      <c r="T41" s="10"/>
-      <c r="U41" s="9"/>
+      <c r="T41" s="10">
+        <v>7</v>
+      </c>
+      <c r="U41" s="10">
+        <v>10</v>
+      </c>
       <c r="V41" s="9"/>
       <c r="W41" s="9"/>
       <c r="X41" s="9"/>
@@ -3728,15 +3874,19 @@
         <v>10</v>
       </c>
       <c r="P42" s="10"/>
-      <c r="Q42" s="31">
+      <c r="Q42" s="28">
         <v>4</v>
       </c>
       <c r="R42" s="10">
         <v>10</v>
       </c>
       <c r="S42" s="10"/>
-      <c r="T42" s="10"/>
-      <c r="U42" s="9"/>
+      <c r="T42" s="10">
+        <v>7</v>
+      </c>
+      <c r="U42" s="10">
+        <v>7</v>
+      </c>
       <c r="V42" s="9"/>
       <c r="W42" s="9"/>
       <c r="X42" s="9"/>
@@ -3789,7 +3939,7 @@
       <c r="P43" s="10">
         <v>9</v>
       </c>
-      <c r="Q43" s="31">
+      <c r="Q43" s="28">
         <v>4</v>
       </c>
       <c r="R43" s="10">
@@ -3798,8 +3948,12 @@
       <c r="S43" s="10">
         <v>5</v>
       </c>
-      <c r="T43" s="10"/>
-      <c r="U43" s="9"/>
+      <c r="T43" s="10">
+        <v>8</v>
+      </c>
+      <c r="U43" s="10">
+        <v>4</v>
+      </c>
       <c r="V43" s="9"/>
       <c r="W43" s="9"/>
       <c r="X43" s="9"/>
@@ -3852,7 +4006,7 @@
       <c r="P44" s="10">
         <v>5</v>
       </c>
-      <c r="Q44" s="31">
+      <c r="Q44" s="28">
         <v>4</v>
       </c>
       <c r="R44" s="10">
@@ -3861,8 +4015,12 @@
       <c r="S44" s="10">
         <v>10</v>
       </c>
-      <c r="T44" s="10"/>
-      <c r="U44" s="9"/>
+      <c r="T44" s="10">
+        <v>10</v>
+      </c>
+      <c r="U44" s="10">
+        <v>10</v>
+      </c>
       <c r="V44" s="9"/>
       <c r="W44" s="9"/>
       <c r="X44" s="9"/>
@@ -3915,7 +4073,7 @@
       <c r="P45" s="10">
         <v>9</v>
       </c>
-      <c r="Q45" s="31">
+      <c r="Q45" s="28">
         <v>18</v>
       </c>
       <c r="R45" s="10">
@@ -3924,8 +4082,12 @@
       <c r="S45" s="10">
         <v>10</v>
       </c>
-      <c r="T45" s="10"/>
-      <c r="U45" s="9"/>
+      <c r="T45" s="10">
+        <v>10</v>
+      </c>
+      <c r="U45" s="10">
+        <v>9</v>
+      </c>
       <c r="V45" s="9"/>
       <c r="W45" s="9"/>
       <c r="X45" s="9"/>
@@ -3978,7 +4140,7 @@
       <c r="P46" s="10">
         <v>10</v>
       </c>
-      <c r="Q46" s="31">
+      <c r="Q46" s="28">
         <v>3</v>
       </c>
       <c r="R46" s="10">
@@ -3987,8 +4149,12 @@
       <c r="S46" s="10">
         <v>10</v>
       </c>
-      <c r="T46" s="10"/>
-      <c r="U46" s="9"/>
+      <c r="T46" s="10">
+        <v>10</v>
+      </c>
+      <c r="U46" s="10">
+        <v>10</v>
+      </c>
       <c r="V46" s="9"/>
       <c r="W46" s="9"/>
       <c r="X46" s="9"/>
@@ -4041,7 +4207,7 @@
       <c r="P47" s="10">
         <v>10</v>
       </c>
-      <c r="Q47" s="31">
+      <c r="Q47" s="28">
         <v>13</v>
       </c>
       <c r="R47" s="10">
@@ -4050,8 +4216,12 @@
       <c r="S47" s="10">
         <v>10</v>
       </c>
-      <c r="T47" s="10"/>
-      <c r="U47" s="9"/>
+      <c r="T47" s="10">
+        <v>7</v>
+      </c>
+      <c r="U47" s="10">
+        <v>10</v>
+      </c>
       <c r="V47" s="9"/>
       <c r="W47" s="9"/>
       <c r="X47" s="9"/>
@@ -4104,7 +4274,7 @@
       <c r="P48" s="10">
         <v>10</v>
       </c>
-      <c r="Q48" s="31">
+      <c r="Q48" s="28">
         <v>6</v>
       </c>
       <c r="R48" s="10">
@@ -4113,8 +4283,12 @@
       <c r="S48" s="10">
         <v>10</v>
       </c>
-      <c r="T48" s="10"/>
-      <c r="U48" s="9"/>
+      <c r="T48" s="10">
+        <v>9</v>
+      </c>
+      <c r="U48" s="10">
+        <v>10</v>
+      </c>
       <c r="V48" s="9"/>
       <c r="W48" s="9"/>
       <c r="X48" s="9"/>
@@ -4167,7 +4341,7 @@
       <c r="P49" s="10">
         <v>10</v>
       </c>
-      <c r="Q49" s="31">
+      <c r="Q49" s="28">
         <v>21</v>
       </c>
       <c r="R49" s="10">
@@ -4176,8 +4350,12 @@
       <c r="S49" s="10">
         <v>10</v>
       </c>
-      <c r="T49" s="10"/>
-      <c r="U49" s="9"/>
+      <c r="T49" s="10">
+        <v>7</v>
+      </c>
+      <c r="U49" s="10">
+        <v>7</v>
+      </c>
       <c r="V49" s="9"/>
       <c r="W49" s="9"/>
       <c r="X49" s="9"/>
@@ -4230,7 +4408,7 @@
       <c r="P50" s="10">
         <v>10</v>
       </c>
-      <c r="Q50" s="31">
+      <c r="Q50" s="28">
         <v>20</v>
       </c>
       <c r="R50" s="10">
@@ -4239,8 +4417,12 @@
       <c r="S50" s="10">
         <v>10</v>
       </c>
-      <c r="T50" s="10"/>
-      <c r="U50" s="9"/>
+      <c r="T50" s="10">
+        <v>7</v>
+      </c>
+      <c r="U50" s="10">
+        <v>10</v>
+      </c>
       <c r="V50" s="9"/>
       <c r="W50" s="9"/>
       <c r="X50" s="9"/>
@@ -4291,15 +4473,19 @@
         <v>10</v>
       </c>
       <c r="P51" s="10"/>
-      <c r="Q51" s="31">
+      <c r="Q51" s="28">
         <v>4</v>
       </c>
       <c r="R51" s="10">
         <v>4</v>
       </c>
       <c r="S51" s="10"/>
-      <c r="T51" s="10"/>
-      <c r="U51" s="9"/>
+      <c r="T51" s="10">
+        <v>7</v>
+      </c>
+      <c r="U51" s="10">
+        <v>3</v>
+      </c>
       <c r="V51" s="9"/>
       <c r="W51" s="9"/>
       <c r="X51" s="9"/>
@@ -4352,7 +4538,7 @@
       <c r="P52" s="10">
         <v>8</v>
       </c>
-      <c r="Q52" s="31">
+      <c r="Q52" s="28">
         <v>22</v>
       </c>
       <c r="R52" s="10">
@@ -4361,8 +4547,12 @@
       <c r="S52" s="10">
         <v>10</v>
       </c>
-      <c r="T52" s="10"/>
-      <c r="U52" s="9"/>
+      <c r="T52" s="10">
+        <v>5</v>
+      </c>
+      <c r="U52" s="10">
+        <v>10</v>
+      </c>
       <c r="V52" s="9"/>
       <c r="W52" s="9"/>
       <c r="X52" s="9"/>
@@ -4415,7 +4605,7 @@
       <c r="P53" s="10">
         <v>10</v>
       </c>
-      <c r="Q53" s="31">
+      <c r="Q53" s="28">
         <v>19</v>
       </c>
       <c r="R53" s="10">
@@ -4424,8 +4614,10 @@
       <c r="S53" s="10">
         <v>10</v>
       </c>
-      <c r="T53" s="10"/>
-      <c r="U53" s="9"/>
+      <c r="T53" s="10">
+        <v>10</v>
+      </c>
+      <c r="U53" s="10"/>
       <c r="V53" s="9"/>
       <c r="W53" s="9"/>
       <c r="X53" s="9"/>
@@ -4433,7 +4625,10 @@
       <c r="Z53" s="9"/>
     </row>
     <row r="54" spans="2:26">
-      <c r="Q54" s="23" t="s">
+      <c r="Q54" s="21" t="s">
+        <v>309</v>
+      </c>
+      <c r="T54" s="8" t="s">
         <v>309</v>
       </c>
     </row>
@@ -4466,8 +4661,11 @@
     <col min="4" max="4" width="3.796875" style="12" customWidth="1"/>
     <col min="5" max="5" width="3.796875" customWidth="1"/>
     <col min="6" max="6" width="3.796875" style="18" customWidth="1"/>
-    <col min="7" max="7" width="3.796875" style="20" customWidth="1"/>
-    <col min="8" max="14" width="3.796875" customWidth="1"/>
+    <col min="7" max="7" width="3.796875" style="8" customWidth="1"/>
+    <col min="8" max="8" width="3.796875" customWidth="1"/>
+    <col min="9" max="9" width="3.796875" style="36" customWidth="1"/>
+    <col min="10" max="10" width="3.796875" style="8" customWidth="1"/>
+    <col min="11" max="14" width="3.796875" customWidth="1"/>
     <col min="15" max="15" width="8.796875" customWidth="1"/>
     <col min="16" max="26" width="4.6484375" customWidth="1"/>
   </cols>
@@ -4488,43 +4686,47 @@
       <c r="F6" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="G6" s="24">
+      <c r="G6" s="34">
         <v>46258</v>
       </c>
-      <c r="H6" s="37">
+      <c r="H6" s="34">
         <v>46265</v>
       </c>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
+      <c r="I6" s="37">
+        <v>25460</v>
+      </c>
+      <c r="J6" s="39" t="s">
+        <v>312</v>
+      </c>
       <c r="K6" s="17"/>
       <c r="L6" s="17"/>
       <c r="M6" s="17"/>
       <c r="N6" s="17"/>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="25" t="str">
+      <c r="A7" s="22" t="str">
         <f>Exercise!B7</f>
         <v>ลำดับที่</v>
       </c>
-      <c r="B7" s="25" t="str">
+      <c r="B7" s="22" t="str">
         <f>Exercise!C7</f>
         <v>รหัสนิสิต</v>
       </c>
-      <c r="C7" s="25" t="str">
+      <c r="C7" s="22" t="str">
         <f>Exercise!D7</f>
         <v>ชื่อ-นามสกุล</v>
       </c>
-      <c r="D7" s="26"/>
-      <c r="E7" s="26"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="26"/>
-      <c r="I7" s="26"/>
-      <c r="J7" s="26"/>
-      <c r="K7" s="26"/>
-      <c r="L7" s="26"/>
-      <c r="M7" s="26"/>
-      <c r="N7" s="26"/>
+      <c r="D7" s="23"/>
+      <c r="E7" s="23"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="23"/>
+      <c r="I7" s="38"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="23"/>
+      <c r="L7" s="23"/>
+      <c r="M7" s="23"/>
+      <c r="N7" s="23"/>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="9" t="str">
@@ -4546,12 +4748,14 @@
       <c r="F8" s="14">
         <v>1</v>
       </c>
-      <c r="G8" s="21"/>
+      <c r="G8" s="10"/>
       <c r="H8" s="9">
         <v>1</v>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="9"/>
+      <c r="I8" s="38"/>
+      <c r="J8" s="10">
+        <v>1</v>
+      </c>
       <c r="K8" s="9"/>
       <c r="L8" s="9"/>
       <c r="M8" s="9"/>
@@ -4575,14 +4779,18 @@
         <v>1</v>
       </c>
       <c r="F9" s="14"/>
-      <c r="G9" s="21">
+      <c r="G9" s="10">
         <v>1</v>
       </c>
       <c r="H9" s="9">
         <v>1</v>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
+      <c r="I9" s="38">
+        <v>1</v>
+      </c>
+      <c r="J9" s="10">
+        <v>1</v>
+      </c>
       <c r="K9" s="9"/>
       <c r="L9" s="9"/>
       <c r="M9" s="9"/>
@@ -4606,12 +4814,14 @@
         <v>1</v>
       </c>
       <c r="F10" s="14"/>
-      <c r="G10" s="21"/>
+      <c r="G10" s="10"/>
       <c r="H10" s="9">
         <v>1</v>
       </c>
-      <c r="I10" s="9"/>
-      <c r="J10" s="9"/>
+      <c r="I10" s="38"/>
+      <c r="J10" s="10">
+        <v>1</v>
+      </c>
       <c r="K10" s="9"/>
       <c r="L10" s="9"/>
       <c r="M10" s="9"/>
@@ -4639,14 +4849,18 @@
       <c r="F11" s="14">
         <v>1</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="10">
         <v>1</v>
       </c>
       <c r="H11" s="9">
         <v>1</v>
       </c>
-      <c r="I11" s="9"/>
-      <c r="J11" s="9"/>
+      <c r="I11" s="38">
+        <v>1</v>
+      </c>
+      <c r="J11" s="10">
+        <v>1</v>
+      </c>
       <c r="K11" s="9"/>
       <c r="L11" s="9"/>
       <c r="M11" s="9"/>
@@ -4674,14 +4888,18 @@
       <c r="F12" s="14">
         <v>1</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="10">
         <v>1</v>
       </c>
       <c r="H12" s="9">
         <v>1</v>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="9"/>
+      <c r="I12" s="38">
+        <v>1</v>
+      </c>
+      <c r="J12" s="10">
+        <v>1</v>
+      </c>
       <c r="K12" s="9"/>
       <c r="L12" s="9"/>
       <c r="M12" s="9"/>
@@ -4705,14 +4923,18 @@
         <v>1</v>
       </c>
       <c r="F13" s="14"/>
-      <c r="G13" s="21">
+      <c r="G13" s="10">
         <v>1</v>
       </c>
       <c r="H13" s="9">
         <v>1</v>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="9"/>
+      <c r="I13" s="38">
+        <v>1</v>
+      </c>
+      <c r="J13" s="10">
+        <v>1</v>
+      </c>
       <c r="K13" s="9"/>
       <c r="L13" s="9"/>
       <c r="M13" s="9"/>
@@ -4738,12 +4960,16 @@
       <c r="F14" s="14">
         <v>1</v>
       </c>
-      <c r="G14" s="21">
+      <c r="G14" s="10">
         <v>1</v>
       </c>
       <c r="H14" s="9"/>
-      <c r="I14" s="9"/>
-      <c r="J14" s="9"/>
+      <c r="I14" s="38">
+        <v>1</v>
+      </c>
+      <c r="J14" s="10">
+        <v>1</v>
+      </c>
       <c r="K14" s="9"/>
       <c r="L14" s="9"/>
       <c r="M14" s="9"/>
@@ -4771,14 +4997,18 @@
       <c r="F15" s="14">
         <v>1</v>
       </c>
-      <c r="G15" s="21">
+      <c r="G15" s="10">
         <v>1</v>
       </c>
       <c r="H15" s="9">
         <v>1</v>
       </c>
-      <c r="I15" s="9"/>
-      <c r="J15" s="9"/>
+      <c r="I15" s="38">
+        <v>1</v>
+      </c>
+      <c r="J15" s="10">
+        <v>1</v>
+      </c>
       <c r="K15" s="9"/>
       <c r="L15" s="9"/>
       <c r="M15" s="9"/>
@@ -4806,14 +5036,18 @@
       <c r="F16" s="14">
         <v>1</v>
       </c>
-      <c r="G16" s="21">
+      <c r="G16" s="10">
         <v>1</v>
       </c>
       <c r="H16" s="9">
         <v>1</v>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="9"/>
+      <c r="I16" s="38">
+        <v>1</v>
+      </c>
+      <c r="J16" s="10">
+        <v>1</v>
+      </c>
       <c r="K16" s="9"/>
       <c r="L16" s="9"/>
       <c r="M16" s="9"/>
@@ -4841,14 +5075,18 @@
       <c r="F17" s="14">
         <v>1</v>
       </c>
-      <c r="G17" s="21">
+      <c r="G17" s="10">
         <v>1</v>
       </c>
       <c r="H17" s="9">
         <v>1</v>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="9"/>
+      <c r="I17" s="38">
+        <v>1</v>
+      </c>
+      <c r="J17" s="10">
+        <v>1</v>
+      </c>
       <c r="K17" s="9"/>
       <c r="L17" s="9"/>
       <c r="M17" s="9"/>
@@ -4874,14 +5112,18 @@
       <c r="F18" s="14">
         <v>1</v>
       </c>
-      <c r="G18" s="21">
+      <c r="G18" s="10">
         <v>1</v>
       </c>
       <c r="H18" s="9">
         <v>1</v>
       </c>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
+      <c r="I18" s="38">
+        <v>1</v>
+      </c>
+      <c r="J18" s="10">
+        <v>1</v>
+      </c>
       <c r="K18" s="9"/>
       <c r="L18" s="9"/>
       <c r="M18" s="9"/>
@@ -4905,14 +5147,18 @@
         <v>1</v>
       </c>
       <c r="F19" s="14"/>
-      <c r="G19" s="21">
+      <c r="G19" s="10">
         <v>1</v>
       </c>
       <c r="H19" s="9">
         <v>1</v>
       </c>
-      <c r="I19" s="9"/>
-      <c r="J19" s="9"/>
+      <c r="I19" s="38">
+        <v>1</v>
+      </c>
+      <c r="J19" s="10">
+        <v>1</v>
+      </c>
       <c r="K19" s="9"/>
       <c r="L19" s="9"/>
       <c r="M19" s="9"/>
@@ -4936,14 +5182,18 @@
       <c r="F20" s="14">
         <v>1</v>
       </c>
-      <c r="G20" s="21">
+      <c r="G20" s="10">
         <v>1</v>
       </c>
       <c r="H20" s="9">
         <v>1</v>
       </c>
-      <c r="I20" s="9"/>
-      <c r="J20" s="9"/>
+      <c r="I20" s="38">
+        <v>1</v>
+      </c>
+      <c r="J20" s="10">
+        <v>1</v>
+      </c>
       <c r="K20" s="9"/>
       <c r="L20" s="9"/>
       <c r="M20" s="9"/>
@@ -4969,10 +5219,12 @@
         <v>1</v>
       </c>
       <c r="F21" s="14"/>
-      <c r="G21" s="21"/>
+      <c r="G21" s="10"/>
       <c r="H21" s="9"/>
-      <c r="I21" s="9"/>
-      <c r="J21" s="9"/>
+      <c r="I21" s="38"/>
+      <c r="J21" s="10">
+        <v>1</v>
+      </c>
       <c r="K21" s="9"/>
       <c r="L21" s="9"/>
       <c r="M21" s="9"/>
@@ -5000,14 +5252,16 @@
       <c r="F22" s="14">
         <v>1</v>
       </c>
-      <c r="G22" s="21">
+      <c r="G22" s="10">
         <v>1</v>
       </c>
       <c r="H22" s="9">
         <v>1</v>
       </c>
-      <c r="I22" s="9"/>
-      <c r="J22" s="9"/>
+      <c r="I22" s="38">
+        <v>1</v>
+      </c>
+      <c r="J22" s="10"/>
       <c r="K22" s="9"/>
       <c r="L22" s="9"/>
       <c r="M22" s="9"/>
@@ -5035,14 +5289,18 @@
       <c r="F23" s="14">
         <v>1</v>
       </c>
-      <c r="G23" s="21">
+      <c r="G23" s="10">
         <v>1</v>
       </c>
       <c r="H23" s="9">
         <v>1</v>
       </c>
-      <c r="I23" s="9"/>
-      <c r="J23" s="9"/>
+      <c r="I23" s="38">
+        <v>1</v>
+      </c>
+      <c r="J23" s="10">
+        <v>1</v>
+      </c>
       <c r="K23" s="9"/>
       <c r="L23" s="9"/>
       <c r="M23" s="9"/>
@@ -5070,14 +5328,18 @@
       <c r="F24" s="14">
         <v>1</v>
       </c>
-      <c r="G24" s="21">
+      <c r="G24" s="10">
         <v>1</v>
       </c>
       <c r="H24" s="9">
         <v>1</v>
       </c>
-      <c r="I24" s="9"/>
-      <c r="J24" s="9"/>
+      <c r="I24" s="38">
+        <v>1</v>
+      </c>
+      <c r="J24" s="10">
+        <v>1</v>
+      </c>
       <c r="K24" s="9"/>
       <c r="L24" s="9"/>
       <c r="M24" s="9"/>
@@ -5105,14 +5367,18 @@
       <c r="F25" s="14">
         <v>1</v>
       </c>
-      <c r="G25" s="21">
+      <c r="G25" s="10">
         <v>1</v>
       </c>
       <c r="H25" s="9">
         <v>1</v>
       </c>
-      <c r="I25" s="9"/>
-      <c r="J25" s="9"/>
+      <c r="I25" s="38">
+        <v>1</v>
+      </c>
+      <c r="J25" s="10">
+        <v>1</v>
+      </c>
       <c r="K25" s="9"/>
       <c r="L25" s="9"/>
       <c r="M25" s="9"/>
@@ -5140,14 +5406,18 @@
       <c r="F26" s="14">
         <v>1</v>
       </c>
-      <c r="G26" s="21">
+      <c r="G26" s="10">
         <v>1</v>
       </c>
       <c r="H26" s="9">
         <v>1</v>
       </c>
-      <c r="I26" s="9"/>
-      <c r="J26" s="9"/>
+      <c r="I26" s="38">
+        <v>1</v>
+      </c>
+      <c r="J26" s="10">
+        <v>1</v>
+      </c>
       <c r="K26" s="9"/>
       <c r="L26" s="9"/>
       <c r="M26" s="9"/>
@@ -5173,14 +5443,18 @@
       <c r="F27" s="14">
         <v>1</v>
       </c>
-      <c r="G27" s="21">
+      <c r="G27" s="10">
         <v>1</v>
       </c>
       <c r="H27" s="9">
         <v>1</v>
       </c>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
+      <c r="I27" s="38">
+        <v>1</v>
+      </c>
+      <c r="J27" s="10">
+        <v>1</v>
+      </c>
       <c r="K27" s="9"/>
       <c r="L27" s="9"/>
       <c r="M27" s="9"/>
@@ -5206,12 +5480,14 @@
       <c r="F28" s="14">
         <v>1</v>
       </c>
-      <c r="G28" s="21">
+      <c r="G28" s="10">
         <v>1</v>
       </c>
       <c r="H28" s="9"/>
-      <c r="I28" s="9"/>
-      <c r="J28" s="9"/>
+      <c r="I28" s="38">
+        <v>1</v>
+      </c>
+      <c r="J28" s="10"/>
       <c r="K28" s="9"/>
       <c r="L28" s="9"/>
       <c r="M28" s="9"/>
@@ -5239,14 +5515,18 @@
       <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="21">
+      <c r="G29" s="10">
         <v>1</v>
       </c>
       <c r="H29" s="9">
         <v>1</v>
       </c>
-      <c r="I29" s="9"/>
-      <c r="J29" s="9"/>
+      <c r="I29" s="38">
+        <v>1</v>
+      </c>
+      <c r="J29" s="10">
+        <v>1</v>
+      </c>
       <c r="K29" s="9"/>
       <c r="L29" s="9"/>
       <c r="M29" s="9"/>
@@ -5274,14 +5554,18 @@
       <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="21">
+      <c r="G30" s="10">
         <v>1</v>
       </c>
       <c r="H30" s="9">
         <v>1</v>
       </c>
-      <c r="I30" s="9"/>
-      <c r="J30" s="9"/>
+      <c r="I30" s="38">
+        <v>1</v>
+      </c>
+      <c r="J30" s="10">
+        <v>1</v>
+      </c>
       <c r="K30" s="9"/>
       <c r="L30" s="9"/>
       <c r="M30" s="9"/>
@@ -5303,10 +5587,10 @@
       <c r="D31" s="13"/>
       <c r="E31" s="15"/>
       <c r="F31" s="14"/>
-      <c r="G31" s="21"/>
+      <c r="G31" s="10"/>
       <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
+      <c r="I31" s="38"/>
+      <c r="J31" s="10"/>
       <c r="K31" s="9"/>
       <c r="L31" s="9"/>
       <c r="M31" s="9"/>
@@ -5334,14 +5618,18 @@
       <c r="F32" s="14">
         <v>1</v>
       </c>
-      <c r="G32" s="21">
+      <c r="G32" s="10">
         <v>1</v>
       </c>
       <c r="H32" s="9">
         <v>1</v>
       </c>
-      <c r="I32" s="9"/>
-      <c r="J32" s="9"/>
+      <c r="I32" s="38">
+        <v>1</v>
+      </c>
+      <c r="J32" s="10">
+        <v>1</v>
+      </c>
       <c r="K32" s="9"/>
       <c r="L32" s="9"/>
       <c r="M32" s="9"/>
@@ -5367,14 +5655,18 @@
       <c r="F33" s="14">
         <v>1</v>
       </c>
-      <c r="G33" s="21">
+      <c r="G33" s="10">
         <v>1</v>
       </c>
       <c r="H33" s="9">
         <v>1</v>
       </c>
-      <c r="I33" s="9"/>
-      <c r="J33" s="9"/>
+      <c r="I33" s="38">
+        <v>1</v>
+      </c>
+      <c r="J33" s="10">
+        <v>1</v>
+      </c>
       <c r="K33" s="9"/>
       <c r="L33" s="9"/>
       <c r="M33" s="9"/>
@@ -5402,14 +5694,18 @@
       <c r="F34" s="14">
         <v>1</v>
       </c>
-      <c r="G34" s="21">
+      <c r="G34" s="10">
         <v>1</v>
       </c>
       <c r="H34" s="9">
         <v>1</v>
       </c>
-      <c r="I34" s="9"/>
-      <c r="J34" s="9"/>
+      <c r="I34" s="38">
+        <v>1</v>
+      </c>
+      <c r="J34" s="10">
+        <v>1</v>
+      </c>
       <c r="K34" s="9"/>
       <c r="L34" s="9"/>
       <c r="M34" s="9"/>
@@ -5437,14 +5733,18 @@
       <c r="F35" s="14">
         <v>1</v>
       </c>
-      <c r="G35" s="21">
+      <c r="G35" s="10">
         <v>1</v>
       </c>
       <c r="H35" s="9">
         <v>1</v>
       </c>
-      <c r="I35" s="9"/>
-      <c r="J35" s="9"/>
+      <c r="I35" s="38">
+        <v>1</v>
+      </c>
+      <c r="J35" s="10">
+        <v>1</v>
+      </c>
       <c r="K35" s="9"/>
       <c r="L35" s="9"/>
       <c r="M35" s="9"/>
@@ -5472,12 +5772,16 @@
       <c r="F36" s="14">
         <v>1</v>
       </c>
-      <c r="G36" s="21">
+      <c r="G36" s="10">
         <v>1</v>
       </c>
       <c r="H36" s="9"/>
-      <c r="I36" s="9"/>
-      <c r="J36" s="9"/>
+      <c r="I36" s="38">
+        <v>1</v>
+      </c>
+      <c r="J36" s="10">
+        <v>1</v>
+      </c>
       <c r="K36" s="9"/>
       <c r="L36" s="9"/>
       <c r="M36" s="9"/>
@@ -5505,14 +5809,18 @@
       <c r="F37" s="14">
         <v>1</v>
       </c>
-      <c r="G37" s="21">
+      <c r="G37" s="10">
         <v>1</v>
       </c>
       <c r="H37" s="9">
         <v>1</v>
       </c>
-      <c r="I37" s="9"/>
-      <c r="J37" s="9"/>
+      <c r="I37" s="38">
+        <v>1</v>
+      </c>
+      <c r="J37" s="10">
+        <v>1</v>
+      </c>
       <c r="K37" s="9"/>
       <c r="L37" s="9"/>
       <c r="M37" s="9"/>
@@ -5538,14 +5846,18 @@
       <c r="F38" s="14">
         <v>1</v>
       </c>
-      <c r="G38" s="21">
+      <c r="G38" s="10">
         <v>1</v>
       </c>
       <c r="H38" s="9">
         <v>1</v>
       </c>
-      <c r="I38" s="9"/>
-      <c r="J38" s="9"/>
+      <c r="I38" s="38">
+        <v>1</v>
+      </c>
+      <c r="J38" s="10">
+        <v>1</v>
+      </c>
       <c r="K38" s="9"/>
       <c r="L38" s="9"/>
       <c r="M38" s="9"/>
@@ -5573,14 +5885,18 @@
       <c r="F39" s="14">
         <v>1</v>
       </c>
-      <c r="G39" s="21">
+      <c r="G39" s="10">
         <v>1</v>
       </c>
       <c r="H39" s="9">
         <v>1</v>
       </c>
-      <c r="I39" s="9"/>
-      <c r="J39" s="9"/>
+      <c r="I39" s="38">
+        <v>1</v>
+      </c>
+      <c r="J39" s="10">
+        <v>1</v>
+      </c>
       <c r="K39" s="9"/>
       <c r="L39" s="9"/>
       <c r="M39" s="9"/>
@@ -5608,14 +5924,16 @@
       <c r="F40" s="14">
         <v>1</v>
       </c>
-      <c r="G40" s="21">
+      <c r="G40" s="10">
         <v>1</v>
       </c>
       <c r="H40" s="9">
         <v>1</v>
       </c>
-      <c r="I40" s="9"/>
-      <c r="J40" s="9"/>
+      <c r="I40" s="38">
+        <v>1</v>
+      </c>
+      <c r="J40" s="10"/>
       <c r="K40" s="9"/>
       <c r="L40" s="9"/>
       <c r="M40" s="9"/>
@@ -5643,14 +5961,18 @@
       <c r="F41" s="14">
         <v>1</v>
       </c>
-      <c r="G41" s="21">
+      <c r="G41" s="10">
         <v>1</v>
       </c>
       <c r="H41" s="9">
         <v>1</v>
       </c>
-      <c r="I41" s="9"/>
-      <c r="J41" s="9"/>
+      <c r="I41" s="38">
+        <v>1</v>
+      </c>
+      <c r="J41" s="10">
+        <v>1</v>
+      </c>
       <c r="K41" s="9"/>
       <c r="L41" s="9"/>
       <c r="M41" s="9"/>
@@ -5678,14 +6000,18 @@
       <c r="F42" s="14">
         <v>1</v>
       </c>
-      <c r="G42" s="21">
+      <c r="G42" s="10">
         <v>1</v>
       </c>
       <c r="H42" s="9">
         <v>1</v>
       </c>
-      <c r="I42" s="9"/>
-      <c r="J42" s="9"/>
+      <c r="I42" s="38">
+        <v>1</v>
+      </c>
+      <c r="J42" s="10">
+        <v>1</v>
+      </c>
       <c r="K42" s="9"/>
       <c r="L42" s="9"/>
       <c r="M42" s="9"/>
@@ -5713,14 +6039,18 @@
       <c r="F43" s="14">
         <v>1</v>
       </c>
-      <c r="G43" s="21">
+      <c r="G43" s="10">
         <v>1</v>
       </c>
       <c r="H43" s="9">
         <v>1</v>
       </c>
-      <c r="I43" s="9"/>
-      <c r="J43" s="9"/>
+      <c r="I43" s="38">
+        <v>1</v>
+      </c>
+      <c r="J43" s="10">
+        <v>1</v>
+      </c>
       <c r="K43" s="9"/>
       <c r="L43" s="9"/>
       <c r="M43" s="9"/>
@@ -5748,14 +6078,18 @@
       <c r="F44" s="14">
         <v>1</v>
       </c>
-      <c r="G44" s="21">
+      <c r="G44" s="10">
         <v>1</v>
       </c>
       <c r="H44" s="9">
         <v>1</v>
       </c>
-      <c r="I44" s="9"/>
-      <c r="J44" s="9"/>
+      <c r="I44" s="38">
+        <v>1</v>
+      </c>
+      <c r="J44" s="10">
+        <v>1</v>
+      </c>
       <c r="K44" s="9"/>
       <c r="L44" s="9"/>
       <c r="M44" s="9"/>
@@ -5783,14 +6117,18 @@
       <c r="F45" s="14">
         <v>1</v>
       </c>
-      <c r="G45" s="21">
+      <c r="G45" s="10">
         <v>1</v>
       </c>
       <c r="H45" s="9">
         <v>1</v>
       </c>
-      <c r="I45" s="9"/>
-      <c r="J45" s="9"/>
+      <c r="I45" s="38">
+        <v>1</v>
+      </c>
+      <c r="J45" s="10">
+        <v>1</v>
+      </c>
       <c r="K45" s="9"/>
       <c r="L45" s="9"/>
       <c r="M45" s="9"/>
@@ -5818,14 +6156,18 @@
       <c r="F46" s="14">
         <v>1</v>
       </c>
-      <c r="G46" s="21">
+      <c r="G46" s="10">
         <v>1</v>
       </c>
       <c r="H46" s="9">
         <v>1</v>
       </c>
-      <c r="I46" s="9"/>
-      <c r="J46" s="9"/>
+      <c r="I46" s="38">
+        <v>1</v>
+      </c>
+      <c r="J46" s="10">
+        <v>1</v>
+      </c>
       <c r="K46" s="9"/>
       <c r="L46" s="9"/>
       <c r="M46" s="9"/>
@@ -5853,14 +6195,18 @@
       <c r="F47" s="14">
         <v>1</v>
       </c>
-      <c r="G47" s="21">
+      <c r="G47" s="10">
         <v>1</v>
       </c>
       <c r="H47" s="9">
         <v>1</v>
       </c>
-      <c r="I47" s="9"/>
-      <c r="J47" s="9"/>
+      <c r="I47" s="38">
+        <v>1</v>
+      </c>
+      <c r="J47" s="10">
+        <v>1</v>
+      </c>
       <c r="K47" s="9"/>
       <c r="L47" s="9"/>
       <c r="M47" s="9"/>
@@ -5888,14 +6234,18 @@
       <c r="F48" s="14">
         <v>1</v>
       </c>
-      <c r="G48" s="21">
+      <c r="G48" s="10">
         <v>1</v>
       </c>
       <c r="H48" s="9">
         <v>1</v>
       </c>
-      <c r="I48" s="9"/>
-      <c r="J48" s="9"/>
+      <c r="I48" s="38">
+        <v>1</v>
+      </c>
+      <c r="J48" s="10">
+        <v>1</v>
+      </c>
       <c r="K48" s="9"/>
       <c r="L48" s="9"/>
       <c r="M48" s="9"/>
@@ -5923,14 +6273,18 @@
       <c r="F49" s="14">
         <v>1</v>
       </c>
-      <c r="G49" s="21">
+      <c r="G49" s="10">
         <v>1</v>
       </c>
       <c r="H49" s="9">
         <v>1</v>
       </c>
-      <c r="I49" s="9"/>
-      <c r="J49" s="9"/>
+      <c r="I49" s="38">
+        <v>1</v>
+      </c>
+      <c r="J49" s="10">
+        <v>1</v>
+      </c>
       <c r="K49" s="9"/>
       <c r="L49" s="9"/>
       <c r="M49" s="9"/>
@@ -5958,14 +6312,18 @@
       <c r="F50" s="14">
         <v>1</v>
       </c>
-      <c r="G50" s="21">
+      <c r="G50" s="10">
         <v>1</v>
       </c>
       <c r="H50" s="9">
         <v>1</v>
       </c>
-      <c r="I50" s="9"/>
-      <c r="J50" s="9"/>
+      <c r="I50" s="38">
+        <v>1</v>
+      </c>
+      <c r="J50" s="10">
+        <v>1</v>
+      </c>
       <c r="K50" s="9"/>
       <c r="L50" s="9"/>
       <c r="M50" s="9"/>
@@ -5993,14 +6351,18 @@
       <c r="F51" s="14">
         <v>1</v>
       </c>
-      <c r="G51" s="21">
+      <c r="G51" s="10">
         <v>1</v>
       </c>
       <c r="H51" s="9">
         <v>1</v>
       </c>
-      <c r="I51" s="9"/>
-      <c r="J51" s="9"/>
+      <c r="I51" s="38">
+        <v>1</v>
+      </c>
+      <c r="J51" s="10">
+        <v>1</v>
+      </c>
       <c r="K51" s="9"/>
       <c r="L51" s="9"/>
       <c r="M51" s="9"/>
@@ -6028,14 +6390,18 @@
       <c r="F52" s="14">
         <v>1</v>
       </c>
-      <c r="G52" s="21">
+      <c r="G52" s="10">
         <v>1</v>
       </c>
       <c r="H52" s="9">
         <v>1</v>
       </c>
-      <c r="I52" s="9"/>
-      <c r="J52" s="9"/>
+      <c r="I52" s="38">
+        <v>1</v>
+      </c>
+      <c r="J52" s="10">
+        <v>1</v>
+      </c>
       <c r="K52" s="9"/>
       <c r="L52" s="9"/>
       <c r="M52" s="9"/>
@@ -6063,14 +6429,18 @@
       <c r="F53" s="14">
         <v>1</v>
       </c>
-      <c r="G53" s="21">
+      <c r="G53" s="10">
         <v>1</v>
       </c>
       <c r="H53" s="9">
         <v>1</v>
       </c>
-      <c r="I53" s="9"/>
-      <c r="J53" s="9"/>
+      <c r="I53" s="38">
+        <v>1</v>
+      </c>
+      <c r="J53" s="10">
+        <v>1</v>
+      </c>
       <c r="K53" s="9"/>
       <c r="L53" s="9"/>
       <c r="M53" s="9"/>

--- a/Score_Class_2026.xlsx
+++ b/Score_Class_2026.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Phisan\Consultancy\2569-KU_MapProjection\Admin\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0E30FD-9ACC-4D43-81EE-8E4566F2BCED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{282CC403-94E3-4E3A-906D-F370929666F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="39620" yWindow="-7000" windowWidth="18090" windowHeight="20970" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-8600" windowWidth="38620" windowHeight="21100" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Exercise" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="498" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="502" uniqueCount="319">
   <si>
     <t>รายงานแสดงจำนวนนิสิต จำแนกตามหมู่เรียน ภาคต้น ปีการศึกษา 2569</t>
   </si>
@@ -960,9 +960,6 @@
     <t>06-10/8/1969</t>
   </si>
   <si>
-    <t>MidTerm</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -978,7 +975,22 @@
     <t>Ex.9 Mercator vs EqualEarth</t>
   </si>
   <si>
-    <t>Ex. UTM zone 47/48</t>
+    <t>Ex.10 UTM zone 47/48</t>
+  </si>
+  <si>
+    <t>Ex.11 LDP</t>
+  </si>
+  <si>
+    <t>Ex.12 WebMap</t>
+  </si>
+  <si>
+    <t>MidTerm Exam</t>
+  </si>
+  <si>
+    <t>Final Exam</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
   </si>
 </sst>
 </file>
@@ -986,9 +998,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="187" formatCode="B1d\-mmm\-yy"/>
+    <numFmt numFmtId="164" formatCode="B1d\-mmm\-yy"/>
   </numFmts>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
@@ -1055,8 +1067,14 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1084,12 +1102,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1134,7 +1146,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1184,7 +1196,7 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="187" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1194,7 +1206,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1223,19 +1234,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="187" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="187" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1245,7 +1267,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="ปกติ" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1273,7 +1295,7 @@
       <xdr:col>3</xdr:col>
       <xdr:colOff>1313180</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>1420790</xdr:rowOff>
+      <xdr:rowOff>1429860</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1459,85 +1481,85 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:Z56"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="15.6"/>
+  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="15.9"/>
   <cols>
     <col min="1" max="1" width="1" customWidth="1"/>
     <col min="2" max="2" width="6" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
-    <col min="4" max="4" width="20.6484375" customWidth="1"/>
+    <col min="4" max="4" width="20.640625" customWidth="1"/>
     <col min="5" max="6" width="18" hidden="1" customWidth="1"/>
     <col min="7" max="8" width="10" hidden="1" customWidth="1"/>
-    <col min="9" max="11" width="10.796875" hidden="1" customWidth="1"/>
-    <col min="12" max="20" width="4.6484375" style="8" customWidth="1"/>
-    <col min="21" max="21" width="4.796875" style="8" customWidth="1"/>
-    <col min="22" max="26" width="4.796875" customWidth="1"/>
+    <col min="9" max="11" width="10.78515625" hidden="1" customWidth="1"/>
+    <col min="12" max="20" width="4.640625" style="8" customWidth="1"/>
+    <col min="21" max="22" width="4.78515625" style="8" customWidth="1"/>
+    <col min="23" max="26" width="4.78515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:26" ht="16" customHeight="1">
-      <c r="B2" s="40" t="s">
+      <c r="B2" s="42" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="40"/>
-      <c r="D2" s="40"/>
-      <c r="E2" s="40"/>
-      <c r="F2" s="40"/>
-      <c r="G2" s="40"/>
-      <c r="H2" s="40"/>
-      <c r="I2" s="40"/>
-      <c r="J2" s="40"/>
-      <c r="K2" s="40"/>
-      <c r="L2" s="40"/>
-      <c r="M2" s="40"/>
-      <c r="N2" s="40"/>
-      <c r="O2" s="40"/>
-      <c r="P2" s="40"/>
-      <c r="Q2" s="40"/>
-      <c r="R2" s="40"/>
-      <c r="S2" s="40"/>
-      <c r="T2" s="40"/>
-    </row>
-    <row r="3" spans="2:26" ht="18.3" customHeight="1">
-      <c r="B3" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="40"/>
-      <c r="D3" s="40"/>
-      <c r="E3" s="40"/>
-      <c r="F3" s="40"/>
-      <c r="G3" s="40"/>
-      <c r="H3" s="40"/>
-      <c r="I3" s="40"/>
-      <c r="J3" s="40"/>
-      <c r="K3" s="40"/>
-      <c r="L3" s="40"/>
-      <c r="M3" s="40"/>
-      <c r="N3" s="40"/>
-      <c r="O3" s="40"/>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40"/>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-    </row>
-    <row r="4" spans="2:26" ht="26.1" customHeight="1">
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+      <c r="H2" s="42"/>
+      <c r="I2" s="42"/>
+      <c r="J2" s="42"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
+      <c r="M2" s="42"/>
+      <c r="N2" s="42"/>
+      <c r="O2" s="42"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="42"/>
+      <c r="T2" s="42"/>
+    </row>
+    <row r="3" spans="2:26" ht="18.350000000000001" customHeight="1">
+      <c r="B3" s="42" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
+      <c r="G3" s="42"/>
+      <c r="H3" s="42"/>
+      <c r="I3" s="42"/>
+      <c r="J3" s="42"/>
+      <c r="K3" s="42"/>
+      <c r="L3" s="42"/>
+      <c r="M3" s="42"/>
+      <c r="N3" s="42"/>
+      <c r="O3" s="42"/>
+      <c r="P3" s="42"/>
+      <c r="Q3" s="42"/>
+      <c r="R3" s="42"/>
+      <c r="S3" s="42"/>
+      <c r="T3" s="42"/>
+    </row>
+    <row r="4" spans="2:26" ht="26.15" customHeight="1">
       <c r="B4" s="1" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="M4" s="41" t="s">
+      <c r="M4" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="N4" s="41"/>
-      <c r="O4" s="41"/>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="41"/>
-      <c r="R4" s="41"/>
-      <c r="S4" s="41"/>
-      <c r="T4" s="41"/>
-    </row>
-    <row r="5" spans="2:26" ht="18">
+      <c r="N4" s="43"/>
+      <c r="O4" s="43"/>
+      <c r="P4" s="43"/>
+      <c r="Q4" s="43"/>
+      <c r="R4" s="43"/>
+      <c r="S4" s="43"/>
+      <c r="T4" s="43"/>
+    </row>
+    <row r="5" spans="2:26" ht="21">
       <c r="E5" s="1" t="s">
         <v>5</v>
       </c>
@@ -1561,7 +1583,7 @@
       <c r="M6" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="N6" s="25" t="s">
+      <c r="N6" s="24" t="s">
         <v>12</v>
       </c>
       <c r="O6" s="11" t="s">
@@ -1570,28 +1592,34 @@
       <c r="P6" s="11" t="s">
         <v>306</v>
       </c>
-      <c r="Q6" s="26" t="s">
-        <v>308</v>
+      <c r="Q6" s="25" t="s">
+        <v>316</v>
       </c>
       <c r="R6" s="11" t="s">
+        <v>309</v>
+      </c>
+      <c r="S6" s="11" t="s">
         <v>310</v>
       </c>
-      <c r="S6" s="11" t="s">
-        <v>311</v>
-      </c>
       <c r="T6" s="11" t="s">
+        <v>312</v>
+      </c>
+      <c r="U6" s="11" t="s">
         <v>313</v>
       </c>
-      <c r="U6" s="11" t="s">
+      <c r="V6" s="11" t="s">
         <v>314</v>
       </c>
-      <c r="V6" s="9"/>
-      <c r="W6" s="9"/>
-      <c r="X6" s="9"/>
+      <c r="W6" s="11" t="s">
+        <v>315</v>
+      </c>
+      <c r="X6" s="25" t="s">
+        <v>317</v>
+      </c>
       <c r="Y6" s="9"/>
       <c r="Z6" s="9"/>
     </row>
-    <row r="7" spans="2:26" ht="20.399999999999999">
+    <row r="7" spans="2:26" ht="22.75">
       <c r="B7" s="3" t="s">
         <v>13</v>
       </c>
@@ -1637,7 +1665,7 @@
       <c r="P7" s="20">
         <v>10</v>
       </c>
-      <c r="Q7" s="27">
+      <c r="Q7" s="26">
         <v>26</v>
       </c>
       <c r="R7" s="20">
@@ -1652,13 +1680,15 @@
       <c r="U7" s="20">
         <v>10</v>
       </c>
-      <c r="V7" s="9"/>
-      <c r="W7" s="9"/>
-      <c r="X7" s="9"/>
+      <c r="V7" s="20">
+        <v>10</v>
+      </c>
+      <c r="W7" s="20"/>
+      <c r="X7" s="26"/>
       <c r="Y7" s="9"/>
       <c r="Z7" s="9"/>
     </row>
-    <row r="8" spans="2:26" ht="18">
+    <row r="8" spans="2:26" ht="21">
       <c r="B8" s="5" t="s">
         <v>22</v>
       </c>
@@ -1698,7 +1728,7 @@
       <c r="P8" s="10">
         <v>8</v>
       </c>
-      <c r="Q8" s="28">
+      <c r="Q8" s="27">
         <v>10</v>
       </c>
       <c r="R8" s="10">
@@ -1711,13 +1741,15 @@
       <c r="U8" s="10">
         <v>9</v>
       </c>
-      <c r="V8" s="9"/>
+      <c r="V8" s="10">
+        <v>3</v>
+      </c>
       <c r="W8" s="9"/>
       <c r="X8" s="9"/>
       <c r="Y8" s="9"/>
       <c r="Z8" s="9"/>
     </row>
-    <row r="9" spans="2:26" ht="18">
+    <row r="9" spans="2:26" ht="21">
       <c r="B9" s="5" t="s">
         <v>32</v>
       </c>
@@ -1757,7 +1789,7 @@
         <v>10</v>
       </c>
       <c r="P9" s="10"/>
-      <c r="Q9" s="28">
+      <c r="Q9" s="27">
         <v>4</v>
       </c>
       <c r="R9" s="10">
@@ -1772,13 +1804,15 @@
       <c r="U9" s="10">
         <v>9</v>
       </c>
-      <c r="V9" s="9"/>
+      <c r="V9" s="10">
+        <v>9</v>
+      </c>
       <c r="W9" s="9"/>
       <c r="X9" s="9"/>
       <c r="Y9" s="9"/>
       <c r="Z9" s="9"/>
     </row>
-    <row r="10" spans="2:26" ht="18">
+    <row r="10" spans="2:26" ht="21">
       <c r="B10" s="5" t="s">
         <v>38</v>
       </c>
@@ -1820,7 +1854,7 @@
       <c r="P10" s="10">
         <v>8</v>
       </c>
-      <c r="Q10" s="28">
+      <c r="Q10" s="27">
         <v>4</v>
       </c>
       <c r="R10" s="10"/>
@@ -1833,13 +1867,15 @@
       <c r="U10" s="10">
         <v>10</v>
       </c>
-      <c r="V10" s="9"/>
+      <c r="V10" s="10">
+        <v>0</v>
+      </c>
       <c r="W10" s="9"/>
       <c r="X10" s="9"/>
       <c r="Y10" s="9"/>
       <c r="Z10" s="9"/>
     </row>
-    <row r="11" spans="2:26" ht="18">
+    <row r="11" spans="2:26" ht="21">
       <c r="B11" s="5" t="s">
         <v>44</v>
       </c>
@@ -1885,7 +1921,7 @@
       <c r="P11" s="10">
         <v>9</v>
       </c>
-      <c r="Q11" s="28">
+      <c r="Q11" s="27">
         <v>9</v>
       </c>
       <c r="R11" s="10">
@@ -1900,13 +1936,15 @@
       <c r="U11" s="10">
         <v>7</v>
       </c>
-      <c r="V11" s="9"/>
+      <c r="V11" s="10">
+        <v>6</v>
+      </c>
       <c r="W11" s="9"/>
       <c r="X11" s="9"/>
       <c r="Y11" s="9"/>
       <c r="Z11" s="9"/>
     </row>
-    <row r="12" spans="2:26" ht="18">
+    <row r="12" spans="2:26" ht="21">
       <c r="B12" s="5" t="s">
         <v>50</v>
       </c>
@@ -1946,7 +1984,7 @@
       <c r="P12" s="10">
         <v>10</v>
       </c>
-      <c r="Q12" s="28">
+      <c r="Q12" s="27">
         <v>9</v>
       </c>
       <c r="R12" s="10">
@@ -1961,13 +1999,13 @@
       <c r="U12" s="10">
         <v>8</v>
       </c>
-      <c r="V12" s="9"/>
+      <c r="V12" s="10"/>
       <c r="W12" s="9"/>
       <c r="X12" s="9"/>
       <c r="Y12" s="9"/>
       <c r="Z12" s="9"/>
     </row>
-    <row r="13" spans="2:26" ht="18">
+    <row r="13" spans="2:26" ht="21">
       <c r="B13" s="5" t="s">
         <v>56</v>
       </c>
@@ -2003,7 +2041,7 @@
       <c r="N13" s="10"/>
       <c r="O13" s="10"/>
       <c r="P13" s="10"/>
-      <c r="Q13" s="28">
+      <c r="Q13" s="27">
         <v>0</v>
       </c>
       <c r="R13" s="10">
@@ -2018,13 +2056,13 @@
       <c r="U13" s="10">
         <v>9</v>
       </c>
-      <c r="V13" s="9"/>
+      <c r="V13" s="10"/>
       <c r="W13" s="9"/>
       <c r="X13" s="9"/>
       <c r="Y13" s="9"/>
       <c r="Z13" s="9"/>
     </row>
-    <row r="14" spans="2:26" ht="18">
+    <row r="14" spans="2:26" ht="21">
       <c r="B14" s="5" t="s">
         <v>62</v>
       </c>
@@ -2066,7 +2104,7 @@
       <c r="P14" s="10">
         <v>8</v>
       </c>
-      <c r="Q14" s="28">
+      <c r="Q14" s="27">
         <v>2</v>
       </c>
       <c r="R14" s="10">
@@ -2081,13 +2119,15 @@
       <c r="U14" s="10">
         <v>7</v>
       </c>
-      <c r="V14" s="9"/>
+      <c r="V14" s="10">
+        <v>10</v>
+      </c>
       <c r="W14" s="9"/>
       <c r="X14" s="9"/>
       <c r="Y14" s="9"/>
       <c r="Z14" s="9"/>
     </row>
-    <row r="15" spans="2:26" ht="18">
+    <row r="15" spans="2:26" ht="21">
       <c r="B15" s="5" t="s">
         <v>68</v>
       </c>
@@ -2133,7 +2173,7 @@
       <c r="P15" s="10">
         <v>8</v>
       </c>
-      <c r="Q15" s="28">
+      <c r="Q15" s="27">
         <v>11</v>
       </c>
       <c r="R15" s="10">
@@ -2148,13 +2188,15 @@
       <c r="U15" s="10">
         <v>7</v>
       </c>
-      <c r="V15" s="9"/>
+      <c r="V15" s="10">
+        <v>9</v>
+      </c>
       <c r="W15" s="9"/>
       <c r="X15" s="9"/>
       <c r="Y15" s="9"/>
       <c r="Z15" s="9"/>
     </row>
-    <row r="16" spans="2:26" ht="18">
+    <row r="16" spans="2:26" ht="21">
       <c r="B16" s="5" t="s">
         <v>74</v>
       </c>
@@ -2196,7 +2238,7 @@
         <v>5</v>
       </c>
       <c r="P16" s="10"/>
-      <c r="Q16" s="28">
+      <c r="Q16" s="27">
         <v>14</v>
       </c>
       <c r="R16" s="10">
@@ -2211,13 +2253,15 @@
       <c r="U16" s="10">
         <v>6</v>
       </c>
-      <c r="V16" s="9"/>
+      <c r="V16" s="10">
+        <v>6</v>
+      </c>
       <c r="W16" s="9"/>
       <c r="X16" s="9"/>
       <c r="Y16" s="9"/>
       <c r="Z16" s="9"/>
     </row>
-    <row r="17" spans="2:26" ht="18">
+    <row r="17" spans="2:26" ht="21">
       <c r="B17" s="5" t="s">
         <v>80</v>
       </c>
@@ -2263,7 +2307,7 @@
       <c r="P17" s="10">
         <v>10</v>
       </c>
-      <c r="Q17" s="28">
+      <c r="Q17" s="27">
         <v>9</v>
       </c>
       <c r="R17" s="10">
@@ -2278,13 +2322,15 @@
       <c r="U17" s="10">
         <v>6</v>
       </c>
-      <c r="V17" s="9"/>
+      <c r="V17" s="10">
+        <v>10</v>
+      </c>
       <c r="W17" s="9"/>
       <c r="X17" s="9"/>
       <c r="Y17" s="9"/>
       <c r="Z17" s="9"/>
     </row>
-    <row r="18" spans="2:26" ht="18">
+    <row r="18" spans="2:26" ht="21">
       <c r="B18" s="5" t="s">
         <v>86</v>
       </c>
@@ -2326,7 +2372,7 @@
       <c r="P18" s="10">
         <v>9</v>
       </c>
-      <c r="Q18" s="28">
+      <c r="Q18" s="27">
         <v>2</v>
       </c>
       <c r="R18" s="10">
@@ -2341,13 +2387,13 @@
       <c r="U18" s="10">
         <v>10</v>
       </c>
-      <c r="V18" s="9"/>
+      <c r="V18" s="10"/>
       <c r="W18" s="9"/>
       <c r="X18" s="9"/>
       <c r="Y18" s="9"/>
       <c r="Z18" s="9"/>
     </row>
-    <row r="19" spans="2:26" ht="18">
+    <row r="19" spans="2:26" ht="21">
       <c r="B19" s="5" t="s">
         <v>92</v>
       </c>
@@ -2383,7 +2429,7 @@
       <c r="N19" s="10"/>
       <c r="O19" s="10"/>
       <c r="P19" s="10"/>
-      <c r="Q19" s="28">
+      <c r="Q19" s="27">
         <v>0</v>
       </c>
       <c r="R19" s="10">
@@ -2398,13 +2444,13 @@
       <c r="U19" s="10">
         <v>7</v>
       </c>
-      <c r="V19" s="9"/>
+      <c r="V19" s="10"/>
       <c r="W19" s="9"/>
       <c r="X19" s="9"/>
       <c r="Y19" s="9"/>
       <c r="Z19" s="9"/>
     </row>
-    <row r="20" spans="2:26" ht="18">
+    <row r="20" spans="2:26" ht="21">
       <c r="B20" s="5" t="s">
         <v>98</v>
       </c>
@@ -2450,7 +2496,7 @@
       <c r="P20" s="10">
         <v>10</v>
       </c>
-      <c r="Q20" s="28">
+      <c r="Q20" s="27">
         <v>5</v>
       </c>
       <c r="R20" s="10">
@@ -2463,13 +2509,15 @@
       <c r="U20" s="10">
         <v>7</v>
       </c>
-      <c r="V20" s="9"/>
+      <c r="V20" s="10">
+        <v>0</v>
+      </c>
       <c r="W20" s="9"/>
       <c r="X20" s="9"/>
       <c r="Y20" s="9"/>
       <c r="Z20" s="9"/>
     </row>
-    <row r="21" spans="2:26" ht="18">
+    <row r="21" spans="2:26" ht="21">
       <c r="B21" s="5" t="s">
         <v>104</v>
       </c>
@@ -2511,7 +2559,7 @@
         <v>5</v>
       </c>
       <c r="P21" s="10"/>
-      <c r="Q21" s="28">
+      <c r="Q21" s="27">
         <v>6</v>
       </c>
       <c r="R21" s="10"/>
@@ -2524,13 +2572,13 @@
       <c r="U21" s="10">
         <v>8</v>
       </c>
-      <c r="V21" s="9"/>
+      <c r="V21" s="10"/>
       <c r="W21" s="9"/>
       <c r="X21" s="9"/>
       <c r="Y21" s="9"/>
       <c r="Z21" s="9"/>
     </row>
-    <row r="22" spans="2:26" ht="18">
+    <row r="22" spans="2:26" ht="21">
       <c r="B22" s="5" t="s">
         <v>110</v>
       </c>
@@ -2576,7 +2624,7 @@
       <c r="P22" s="10">
         <v>10</v>
       </c>
-      <c r="Q22" s="28">
+      <c r="Q22" s="27">
         <v>2</v>
       </c>
       <c r="R22" s="10">
@@ -2585,15 +2633,21 @@
       <c r="S22" s="10">
         <v>9</v>
       </c>
-      <c r="T22" s="10"/>
-      <c r="U22" s="10"/>
-      <c r="V22" s="9"/>
+      <c r="T22" s="10">
+        <v>7</v>
+      </c>
+      <c r="U22" s="10">
+        <v>10</v>
+      </c>
+      <c r="V22" s="10">
+        <v>0</v>
+      </c>
       <c r="W22" s="9"/>
       <c r="X22" s="9"/>
       <c r="Y22" s="9"/>
       <c r="Z22" s="9"/>
     </row>
-    <row r="23" spans="2:26" ht="18">
+    <row r="23" spans="2:26" ht="21">
       <c r="B23" s="5" t="s">
         <v>116</v>
       </c>
@@ -2639,7 +2693,7 @@
       <c r="P23" s="10">
         <v>10</v>
       </c>
-      <c r="Q23" s="28">
+      <c r="Q23" s="27">
         <v>16</v>
       </c>
       <c r="R23" s="10">
@@ -2654,13 +2708,15 @@
       <c r="U23" s="10">
         <v>10</v>
       </c>
-      <c r="V23" s="9"/>
+      <c r="V23" s="10">
+        <v>0</v>
+      </c>
       <c r="W23" s="9"/>
       <c r="X23" s="9"/>
       <c r="Y23" s="9"/>
       <c r="Z23" s="9"/>
     </row>
-    <row r="24" spans="2:26" ht="18">
+    <row r="24" spans="2:26" ht="21">
       <c r="B24" s="5" t="s">
         <v>122</v>
       </c>
@@ -2706,7 +2762,7 @@
       <c r="P24" s="10">
         <v>10</v>
       </c>
-      <c r="Q24" s="28">
+      <c r="Q24" s="27">
         <v>12</v>
       </c>
       <c r="R24" s="10">
@@ -2721,13 +2777,15 @@
       <c r="U24" s="10">
         <v>10</v>
       </c>
-      <c r="V24" s="9"/>
+      <c r="V24" s="10">
+        <v>0</v>
+      </c>
       <c r="W24" s="9"/>
       <c r="X24" s="9"/>
       <c r="Y24" s="9"/>
       <c r="Z24" s="9"/>
     </row>
-    <row r="25" spans="2:26" ht="18">
+    <row r="25" spans="2:26" ht="21">
       <c r="B25" s="5" t="s">
         <v>128</v>
       </c>
@@ -2773,7 +2831,7 @@
       <c r="P25" s="10">
         <v>10</v>
       </c>
-      <c r="Q25" s="28">
+      <c r="Q25" s="27">
         <v>9</v>
       </c>
       <c r="R25" s="10">
@@ -2788,13 +2846,15 @@
       <c r="U25" s="10">
         <v>8</v>
       </c>
-      <c r="V25" s="9"/>
+      <c r="V25" s="10">
+        <v>0</v>
+      </c>
       <c r="W25" s="9"/>
       <c r="X25" s="9"/>
       <c r="Y25" s="9"/>
       <c r="Z25" s="9"/>
     </row>
-    <row r="26" spans="2:26" ht="18">
+    <row r="26" spans="2:26" ht="21">
       <c r="B26" s="5" t="s">
         <v>134</v>
       </c>
@@ -2840,7 +2900,7 @@
       <c r="P26" s="10">
         <v>10</v>
       </c>
-      <c r="Q26" s="28">
+      <c r="Q26" s="27">
         <v>1</v>
       </c>
       <c r="R26" s="10">
@@ -2855,13 +2915,15 @@
       <c r="U26" s="10">
         <v>8</v>
       </c>
-      <c r="V26" s="9"/>
+      <c r="V26" s="10">
+        <v>10</v>
+      </c>
       <c r="W26" s="9"/>
       <c r="X26" s="9"/>
       <c r="Y26" s="9"/>
       <c r="Z26" s="9"/>
     </row>
-    <row r="27" spans="2:26" ht="18">
+    <row r="27" spans="2:26" ht="21">
       <c r="B27" s="5" t="s">
         <v>140</v>
       </c>
@@ -2905,7 +2967,7 @@
       <c r="P27" s="10">
         <v>10</v>
       </c>
-      <c r="Q27" s="28">
+      <c r="Q27" s="27">
         <v>1</v>
       </c>
       <c r="R27" s="10">
@@ -2920,13 +2982,15 @@
       <c r="U27" s="10">
         <v>10</v>
       </c>
-      <c r="V27" s="9"/>
+      <c r="V27" s="10">
+        <v>10</v>
+      </c>
       <c r="W27" s="9"/>
       <c r="X27" s="9"/>
       <c r="Y27" s="9"/>
       <c r="Z27" s="9"/>
     </row>
-    <row r="28" spans="2:26" ht="18">
+    <row r="28" spans="2:26" ht="21">
       <c r="B28" s="5" t="s">
         <v>146</v>
       </c>
@@ -2968,7 +3032,7 @@
         <v>4</v>
       </c>
       <c r="P28" s="10"/>
-      <c r="Q28" s="28">
+      <c r="Q28" s="27">
         <v>8</v>
       </c>
       <c r="R28" s="10">
@@ -2979,13 +3043,15 @@
       </c>
       <c r="T28" s="10"/>
       <c r="U28" s="10"/>
-      <c r="V28" s="9"/>
+      <c r="V28" s="10">
+        <v>7</v>
+      </c>
       <c r="W28" s="9"/>
       <c r="X28" s="9"/>
       <c r="Y28" s="9"/>
       <c r="Z28" s="9"/>
     </row>
-    <row r="29" spans="2:26" ht="18">
+    <row r="29" spans="2:26" ht="21">
       <c r="B29" s="5" t="s">
         <v>152</v>
       </c>
@@ -3031,7 +3097,7 @@
       <c r="P29" s="10">
         <v>10</v>
       </c>
-      <c r="Q29" s="28">
+      <c r="Q29" s="27">
         <v>9</v>
       </c>
       <c r="R29" s="10">
@@ -3046,13 +3112,15 @@
       <c r="U29" s="10">
         <v>10</v>
       </c>
-      <c r="V29" s="9"/>
+      <c r="V29" s="10">
+        <v>0</v>
+      </c>
       <c r="W29" s="9"/>
       <c r="X29" s="9"/>
       <c r="Y29" s="9"/>
       <c r="Z29" s="9"/>
     </row>
-    <row r="30" spans="2:26" ht="18">
+    <row r="30" spans="2:26" ht="21">
       <c r="B30" s="5" t="s">
         <v>158</v>
       </c>
@@ -3098,7 +3166,7 @@
       <c r="P30" s="10">
         <v>10</v>
       </c>
-      <c r="Q30" s="28">
+      <c r="Q30" s="27">
         <v>11</v>
       </c>
       <c r="R30" s="10">
@@ -3113,60 +3181,62 @@
       <c r="U30" s="10">
         <v>10</v>
       </c>
-      <c r="V30" s="9"/>
+      <c r="V30" s="10">
+        <v>0</v>
+      </c>
       <c r="W30" s="9"/>
       <c r="X30" s="9"/>
       <c r="Y30" s="9"/>
       <c r="Z30" s="9"/>
     </row>
-    <row r="31" spans="2:26" ht="18">
-      <c r="B31" s="29" t="s">
+    <row r="31" spans="2:26" ht="21">
+      <c r="B31" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="C31" s="30" t="s">
+      <c r="C31" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="D31" s="30" t="s">
+      <c r="D31" s="29" t="s">
         <v>166</v>
       </c>
-      <c r="E31" s="30" t="s">
+      <c r="E31" s="29" t="s">
         <v>167</v>
       </c>
-      <c r="F31" s="30" t="s">
+      <c r="F31" s="29" t="s">
         <v>26</v>
       </c>
-      <c r="G31" s="30" t="s">
+      <c r="G31" s="29" t="s">
         <v>27</v>
       </c>
-      <c r="H31" s="30" t="s">
+      <c r="H31" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="I31" s="30" t="s">
+      <c r="I31" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="J31" s="30" t="s">
+      <c r="J31" s="29" t="s">
         <v>168</v>
       </c>
-      <c r="K31" s="31" t="s">
+      <c r="K31" s="30" t="s">
         <v>169</v>
       </c>
-      <c r="L31" s="32"/>
-      <c r="M31" s="32"/>
-      <c r="N31" s="32"/>
-      <c r="O31" s="32"/>
-      <c r="P31" s="32"/>
-      <c r="Q31" s="32"/>
-      <c r="R31" s="32"/>
-      <c r="S31" s="32"/>
-      <c r="T31" s="32"/>
-      <c r="U31" s="32"/>
-      <c r="V31" s="33"/>
-      <c r="W31" s="33"/>
-      <c r="X31" s="33"/>
-      <c r="Y31" s="33"/>
-      <c r="Z31" s="33"/>
-    </row>
-    <row r="32" spans="2:26" ht="18">
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="31"/>
+      <c r="P31" s="31"/>
+      <c r="Q31" s="31"/>
+      <c r="R31" s="31"/>
+      <c r="S31" s="31"/>
+      <c r="T31" s="31"/>
+      <c r="U31" s="31"/>
+      <c r="V31" s="31"/>
+      <c r="W31" s="32"/>
+      <c r="X31" s="32"/>
+      <c r="Y31" s="32"/>
+      <c r="Z31" s="32"/>
+    </row>
+    <row r="32" spans="2:26" ht="21">
       <c r="B32" s="5" t="s">
         <v>29</v>
       </c>
@@ -3212,7 +3282,7 @@
       <c r="P32" s="10">
         <v>10</v>
       </c>
-      <c r="Q32" s="28">
+      <c r="Q32" s="27">
         <v>14</v>
       </c>
       <c r="R32" s="10">
@@ -3227,13 +3297,15 @@
       <c r="U32" s="10">
         <v>7</v>
       </c>
-      <c r="V32" s="9"/>
+      <c r="V32" s="10">
+        <v>6</v>
+      </c>
       <c r="W32" s="9"/>
       <c r="X32" s="9"/>
       <c r="Y32" s="9"/>
       <c r="Z32" s="9"/>
     </row>
-    <row r="33" spans="2:26" ht="18">
+    <row r="33" spans="2:26" ht="21">
       <c r="B33" s="5" t="s">
         <v>175</v>
       </c>
@@ -3277,7 +3349,7 @@
       <c r="P33" s="10">
         <v>10</v>
       </c>
-      <c r="Q33" s="28">
+      <c r="Q33" s="27">
         <v>3</v>
       </c>
       <c r="R33" s="10">
@@ -3290,13 +3362,15 @@
       <c r="U33" s="10">
         <v>10</v>
       </c>
-      <c r="V33" s="9"/>
+      <c r="V33" s="10">
+        <v>10</v>
+      </c>
       <c r="W33" s="9"/>
       <c r="X33" s="9"/>
       <c r="Y33" s="9"/>
       <c r="Z33" s="9"/>
     </row>
-    <row r="34" spans="2:26" ht="18">
+    <row r="34" spans="2:26" ht="21">
       <c r="B34" s="5" t="s">
         <v>181</v>
       </c>
@@ -3357,13 +3431,15 @@
       <c r="U34" s="10">
         <v>10</v>
       </c>
-      <c r="V34" s="9"/>
+      <c r="V34" s="10">
+        <v>7</v>
+      </c>
       <c r="W34" s="9"/>
       <c r="X34" s="9"/>
       <c r="Y34" s="9"/>
       <c r="Z34" s="9"/>
     </row>
-    <row r="35" spans="2:26" ht="18">
+    <row r="35" spans="2:26" ht="21">
       <c r="B35" s="5" t="s">
         <v>187</v>
       </c>
@@ -3409,7 +3485,7 @@
       <c r="P35" s="10">
         <v>10</v>
       </c>
-      <c r="Q35" s="28">
+      <c r="Q35" s="27">
         <v>17</v>
       </c>
       <c r="R35" s="10">
@@ -3424,13 +3500,15 @@
       <c r="U35" s="10">
         <v>9</v>
       </c>
-      <c r="V35" s="9"/>
+      <c r="V35" s="10">
+        <v>0</v>
+      </c>
       <c r="W35" s="9"/>
       <c r="X35" s="9"/>
       <c r="Y35" s="9"/>
       <c r="Z35" s="9"/>
     </row>
-    <row r="36" spans="2:26" ht="18">
+    <row r="36" spans="2:26" ht="21">
       <c r="B36" s="5" t="s">
         <v>193</v>
       </c>
@@ -3476,7 +3554,7 @@
       <c r="P36" s="10">
         <v>10</v>
       </c>
-      <c r="Q36" s="28">
+      <c r="Q36" s="27">
         <v>7</v>
       </c>
       <c r="R36" s="10">
@@ -3491,13 +3569,15 @@
       <c r="U36" s="10">
         <v>7</v>
       </c>
-      <c r="V36" s="9"/>
+      <c r="V36" s="10">
+        <v>10</v>
+      </c>
       <c r="W36" s="9"/>
       <c r="X36" s="9"/>
       <c r="Y36" s="9"/>
       <c r="Z36" s="9"/>
     </row>
-    <row r="37" spans="2:26" ht="18">
+    <row r="37" spans="2:26" ht="21">
       <c r="B37" s="5" t="s">
         <v>199</v>
       </c>
@@ -3543,7 +3623,7 @@
       <c r="P37" s="10">
         <v>9</v>
       </c>
-      <c r="Q37" s="28">
+      <c r="Q37" s="27">
         <v>17</v>
       </c>
       <c r="R37" s="10">
@@ -3558,13 +3638,15 @@
       <c r="U37" s="10">
         <v>6</v>
       </c>
-      <c r="V37" s="9"/>
+      <c r="V37" s="10">
+        <v>0</v>
+      </c>
       <c r="W37" s="9"/>
       <c r="X37" s="9"/>
       <c r="Y37" s="9"/>
       <c r="Z37" s="9"/>
     </row>
-    <row r="38" spans="2:26" ht="18">
+    <row r="38" spans="2:26" ht="21">
       <c r="B38" s="5" t="s">
         <v>205</v>
       </c>
@@ -3608,7 +3690,7 @@
       <c r="P38" s="10">
         <v>10</v>
       </c>
-      <c r="Q38" s="28">
+      <c r="Q38" s="27">
         <v>16</v>
       </c>
       <c r="R38" s="10">
@@ -3623,13 +3705,15 @@
       <c r="U38" s="10">
         <v>8</v>
       </c>
-      <c r="V38" s="9"/>
+      <c r="V38" s="10">
+        <v>0</v>
+      </c>
       <c r="W38" s="9"/>
       <c r="X38" s="9"/>
       <c r="Y38" s="9"/>
       <c r="Z38" s="9"/>
     </row>
-    <row r="39" spans="2:26" ht="18">
+    <row r="39" spans="2:26" ht="21">
       <c r="B39" s="5" t="s">
         <v>211</v>
       </c>
@@ -3675,7 +3759,7 @@
       <c r="P39" s="10">
         <v>10</v>
       </c>
-      <c r="Q39" s="28">
+      <c r="Q39" s="27">
         <v>22</v>
       </c>
       <c r="R39" s="10">
@@ -3690,13 +3774,15 @@
       <c r="U39" s="10">
         <v>10</v>
       </c>
-      <c r="V39" s="9"/>
+      <c r="V39" s="10">
+        <v>10</v>
+      </c>
       <c r="W39" s="9"/>
       <c r="X39" s="9"/>
       <c r="Y39" s="9"/>
       <c r="Z39" s="9"/>
     </row>
-    <row r="40" spans="2:26" ht="18">
+    <row r="40" spans="2:26" ht="21">
       <c r="B40" s="5" t="s">
         <v>217</v>
       </c>
@@ -3742,7 +3828,7 @@
       <c r="P40" s="10">
         <v>10</v>
       </c>
-      <c r="Q40" s="28">
+      <c r="Q40" s="27">
         <v>15</v>
       </c>
       <c r="R40" s="10">
@@ -3757,13 +3843,15 @@
       <c r="U40" s="10">
         <v>10</v>
       </c>
-      <c r="V40" s="9"/>
+      <c r="V40" s="10">
+        <v>8</v>
+      </c>
       <c r="W40" s="9"/>
       <c r="X40" s="9"/>
       <c r="Y40" s="9"/>
       <c r="Z40" s="9"/>
     </row>
-    <row r="41" spans="2:26" ht="18">
+    <row r="41" spans="2:26" ht="21">
       <c r="B41" s="5" t="s">
         <v>223</v>
       </c>
@@ -3809,7 +3897,7 @@
       <c r="P41" s="10">
         <v>10</v>
       </c>
-      <c r="Q41" s="28">
+      <c r="Q41" s="27">
         <v>6</v>
       </c>
       <c r="R41" s="10">
@@ -3824,13 +3912,15 @@
       <c r="U41" s="10">
         <v>10</v>
       </c>
-      <c r="V41" s="9"/>
+      <c r="V41" s="10">
+        <v>0</v>
+      </c>
       <c r="W41" s="9"/>
       <c r="X41" s="9"/>
       <c r="Y41" s="9"/>
       <c r="Z41" s="9"/>
     </row>
-    <row r="42" spans="2:26" ht="18">
+    <row r="42" spans="2:26" ht="21">
       <c r="B42" s="5" t="s">
         <v>229</v>
       </c>
@@ -3874,7 +3964,7 @@
         <v>10</v>
       </c>
       <c r="P42" s="10"/>
-      <c r="Q42" s="28">
+      <c r="Q42" s="27">
         <v>4</v>
       </c>
       <c r="R42" s="10">
@@ -3887,13 +3977,15 @@
       <c r="U42" s="10">
         <v>7</v>
       </c>
-      <c r="V42" s="9"/>
+      <c r="V42" s="10">
+        <v>0</v>
+      </c>
       <c r="W42" s="9"/>
       <c r="X42" s="9"/>
       <c r="Y42" s="9"/>
       <c r="Z42" s="9"/>
     </row>
-    <row r="43" spans="2:26" ht="18">
+    <row r="43" spans="2:26" ht="21">
       <c r="B43" s="5" t="s">
         <v>235</v>
       </c>
@@ -3939,7 +4031,7 @@
       <c r="P43" s="10">
         <v>9</v>
       </c>
-      <c r="Q43" s="28">
+      <c r="Q43" s="27">
         <v>4</v>
       </c>
       <c r="R43" s="10">
@@ -3954,13 +4046,15 @@
       <c r="U43" s="10">
         <v>4</v>
       </c>
-      <c r="V43" s="9"/>
+      <c r="V43" s="10">
+        <v>10</v>
+      </c>
       <c r="W43" s="9"/>
       <c r="X43" s="9"/>
       <c r="Y43" s="9"/>
       <c r="Z43" s="9"/>
     </row>
-    <row r="44" spans="2:26" ht="18">
+    <row r="44" spans="2:26" ht="21">
       <c r="B44" s="5" t="s">
         <v>241</v>
       </c>
@@ -4006,7 +4100,7 @@
       <c r="P44" s="10">
         <v>5</v>
       </c>
-      <c r="Q44" s="28">
+      <c r="Q44" s="27">
         <v>4</v>
       </c>
       <c r="R44" s="10">
@@ -4021,13 +4115,15 @@
       <c r="U44" s="10">
         <v>10</v>
       </c>
-      <c r="V44" s="9"/>
+      <c r="V44" s="10">
+        <v>10</v>
+      </c>
       <c r="W44" s="9"/>
       <c r="X44" s="9"/>
       <c r="Y44" s="9"/>
       <c r="Z44" s="9"/>
     </row>
-    <row r="45" spans="2:26" ht="18">
+    <row r="45" spans="2:26" ht="21">
       <c r="B45" s="5" t="s">
         <v>247</v>
       </c>
@@ -4073,7 +4169,7 @@
       <c r="P45" s="10">
         <v>9</v>
       </c>
-      <c r="Q45" s="28">
+      <c r="Q45" s="27">
         <v>18</v>
       </c>
       <c r="R45" s="10">
@@ -4088,13 +4184,15 @@
       <c r="U45" s="10">
         <v>9</v>
       </c>
-      <c r="V45" s="9"/>
+      <c r="V45" s="10">
+        <v>0</v>
+      </c>
       <c r="W45" s="9"/>
       <c r="X45" s="9"/>
       <c r="Y45" s="9"/>
       <c r="Z45" s="9"/>
     </row>
-    <row r="46" spans="2:26" ht="18">
+    <row r="46" spans="2:26" ht="21">
       <c r="B46" s="5" t="s">
         <v>253</v>
       </c>
@@ -4140,7 +4238,7 @@
       <c r="P46" s="10">
         <v>10</v>
       </c>
-      <c r="Q46" s="28">
+      <c r="Q46" s="27">
         <v>3</v>
       </c>
       <c r="R46" s="10">
@@ -4155,13 +4253,15 @@
       <c r="U46" s="10">
         <v>10</v>
       </c>
-      <c r="V46" s="9"/>
+      <c r="V46" s="10">
+        <v>9</v>
+      </c>
       <c r="W46" s="9"/>
       <c r="X46" s="9"/>
       <c r="Y46" s="9"/>
       <c r="Z46" s="9"/>
     </row>
-    <row r="47" spans="2:26" ht="18">
+    <row r="47" spans="2:26" ht="21">
       <c r="B47" s="5" t="s">
         <v>259</v>
       </c>
@@ -4207,7 +4307,7 @@
       <c r="P47" s="10">
         <v>10</v>
       </c>
-      <c r="Q47" s="28">
+      <c r="Q47" s="27">
         <v>13</v>
       </c>
       <c r="R47" s="10">
@@ -4222,13 +4322,15 @@
       <c r="U47" s="10">
         <v>10</v>
       </c>
-      <c r="V47" s="9"/>
+      <c r="V47" s="10">
+        <v>0</v>
+      </c>
       <c r="W47" s="9"/>
       <c r="X47" s="9"/>
       <c r="Y47" s="9"/>
       <c r="Z47" s="9"/>
     </row>
-    <row r="48" spans="2:26" ht="18">
+    <row r="48" spans="2:26" ht="21">
       <c r="B48" s="5" t="s">
         <v>265</v>
       </c>
@@ -4274,7 +4376,7 @@
       <c r="P48" s="10">
         <v>10</v>
       </c>
-      <c r="Q48" s="28">
+      <c r="Q48" s="27">
         <v>6</v>
       </c>
       <c r="R48" s="10">
@@ -4289,13 +4391,15 @@
       <c r="U48" s="10">
         <v>10</v>
       </c>
-      <c r="V48" s="9"/>
+      <c r="V48" s="10">
+        <v>10</v>
+      </c>
       <c r="W48" s="9"/>
       <c r="X48" s="9"/>
       <c r="Y48" s="9"/>
       <c r="Z48" s="9"/>
     </row>
-    <row r="49" spans="2:26" ht="18">
+    <row r="49" spans="2:26" ht="21">
       <c r="B49" s="5" t="s">
         <v>271</v>
       </c>
@@ -4341,7 +4445,7 @@
       <c r="P49" s="10">
         <v>10</v>
       </c>
-      <c r="Q49" s="28">
+      <c r="Q49" s="27">
         <v>21</v>
       </c>
       <c r="R49" s="10">
@@ -4356,13 +4460,15 @@
       <c r="U49" s="10">
         <v>7</v>
       </c>
-      <c r="V49" s="9"/>
+      <c r="V49" s="10">
+        <v>0</v>
+      </c>
       <c r="W49" s="9"/>
       <c r="X49" s="9"/>
       <c r="Y49" s="9"/>
       <c r="Z49" s="9"/>
     </row>
-    <row r="50" spans="2:26" ht="18">
+    <row r="50" spans="2:26" ht="21">
       <c r="B50" s="5" t="s">
         <v>277</v>
       </c>
@@ -4408,7 +4514,7 @@
       <c r="P50" s="10">
         <v>10</v>
       </c>
-      <c r="Q50" s="28">
+      <c r="Q50" s="27">
         <v>20</v>
       </c>
       <c r="R50" s="10">
@@ -4423,13 +4529,13 @@
       <c r="U50" s="10">
         <v>10</v>
       </c>
-      <c r="V50" s="9"/>
+      <c r="V50" s="10"/>
       <c r="W50" s="9"/>
       <c r="X50" s="9"/>
       <c r="Y50" s="9"/>
       <c r="Z50" s="9"/>
     </row>
-    <row r="51" spans="2:26" ht="18">
+    <row r="51" spans="2:26" ht="21">
       <c r="B51" s="5" t="s">
         <v>283</v>
       </c>
@@ -4473,7 +4579,7 @@
         <v>10</v>
       </c>
       <c r="P51" s="10"/>
-      <c r="Q51" s="28">
+      <c r="Q51" s="27">
         <v>4</v>
       </c>
       <c r="R51" s="10">
@@ -4486,13 +4592,13 @@
       <c r="U51" s="10">
         <v>3</v>
       </c>
-      <c r="V51" s="9"/>
+      <c r="V51" s="10"/>
       <c r="W51" s="9"/>
       <c r="X51" s="9"/>
       <c r="Y51" s="9"/>
       <c r="Z51" s="9"/>
     </row>
-    <row r="52" spans="2:26" ht="18">
+    <row r="52" spans="2:26" ht="21">
       <c r="B52" s="5" t="s">
         <v>289</v>
       </c>
@@ -4538,7 +4644,7 @@
       <c r="P52" s="10">
         <v>8</v>
       </c>
-      <c r="Q52" s="28">
+      <c r="Q52" s="27">
         <v>22</v>
       </c>
       <c r="R52" s="10">
@@ -4553,13 +4659,15 @@
       <c r="U52" s="10">
         <v>10</v>
       </c>
-      <c r="V52" s="9"/>
+      <c r="V52" s="10">
+        <v>0</v>
+      </c>
       <c r="W52" s="9"/>
       <c r="X52" s="9"/>
       <c r="Y52" s="9"/>
       <c r="Z52" s="9"/>
     </row>
-    <row r="53" spans="2:26" ht="18">
+    <row r="53" spans="2:26" ht="21">
       <c r="B53" s="5" t="s">
         <v>295</v>
       </c>
@@ -4605,7 +4713,7 @@
       <c r="P53" s="10">
         <v>10</v>
       </c>
-      <c r="Q53" s="28">
+      <c r="Q53" s="27">
         <v>19</v>
       </c>
       <c r="R53" s="10">
@@ -4617,8 +4725,12 @@
       <c r="T53" s="10">
         <v>10</v>
       </c>
-      <c r="U53" s="10"/>
-      <c r="V53" s="9"/>
+      <c r="U53" s="10">
+        <v>10</v>
+      </c>
+      <c r="V53" s="10">
+        <v>8</v>
+      </c>
       <c r="W53" s="9"/>
       <c r="X53" s="9"/>
       <c r="Y53" s="9"/>
@@ -4626,13 +4738,16 @@
     </row>
     <row r="54" spans="2:26">
       <c r="Q54" s="21" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="T54" s="8" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="56" spans="2:26" ht="18">
+        <v>308</v>
+      </c>
+      <c r="V54" s="8" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="56" spans="2:26" ht="21">
       <c r="B56" s="1"/>
       <c r="G56" s="2" t="s">
         <v>301</v>
@@ -4652,27 +4767,27 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBE402B1-12FE-47A6-B362-96D0109E0A3C}">
-  <dimension ref="A5:N53"/>
-  <sheetFormatPr defaultRowHeight="15.6"/>
+  <dimension ref="A5:L53"/>
+  <sheetFormatPr defaultRowHeight="15.9"/>
   <cols>
-    <col min="1" max="1" width="6.94921875" customWidth="1"/>
-    <col min="2" max="2" width="16.19921875" customWidth="1"/>
-    <col min="3" max="3" width="31.046875" customWidth="1"/>
-    <col min="4" max="4" width="3.796875" style="12" customWidth="1"/>
-    <col min="5" max="5" width="3.796875" customWidth="1"/>
-    <col min="6" max="6" width="3.796875" style="18" customWidth="1"/>
-    <col min="7" max="7" width="3.796875" style="8" customWidth="1"/>
-    <col min="8" max="8" width="3.796875" customWidth="1"/>
-    <col min="9" max="9" width="3.796875" style="36" customWidth="1"/>
-    <col min="10" max="10" width="3.796875" style="8" customWidth="1"/>
-    <col min="11" max="14" width="3.796875" customWidth="1"/>
-    <col min="15" max="15" width="8.796875" customWidth="1"/>
-    <col min="16" max="26" width="4.6484375" customWidth="1"/>
+    <col min="1" max="1" width="6.92578125" style="8" customWidth="1"/>
+    <col min="2" max="2" width="16.2109375" customWidth="1"/>
+    <col min="3" max="3" width="31.0703125" customWidth="1"/>
+    <col min="4" max="4" width="3.78515625" style="12" customWidth="1"/>
+    <col min="5" max="5" width="3.78515625" customWidth="1"/>
+    <col min="6" max="6" width="3.78515625" style="18" customWidth="1"/>
+    <col min="7" max="7" width="3.78515625" style="8" customWidth="1"/>
+    <col min="8" max="8" width="3.78515625" customWidth="1"/>
+    <col min="9" max="9" width="3.78515625" style="36" customWidth="1"/>
+    <col min="10" max="10" width="3.78515625" style="8" customWidth="1"/>
+    <col min="11" max="12" width="3.78515625" customWidth="1"/>
+    <col min="13" max="13" width="3.85546875" customWidth="1"/>
+    <col min="14" max="24" width="4.640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:14" ht="19.2" customHeight="1"/>
-    <row r="6" spans="1:14" ht="69.599999999999994" customHeight="1">
-      <c r="A6" s="9"/>
+    <row r="5" spans="1:12" ht="19.2" customHeight="1"/>
+    <row r="6" spans="1:12" ht="69.650000000000006" customHeight="1">
+      <c r="A6" s="10"/>
       <c r="B6" s="9"/>
       <c r="C6" s="10" t="s">
         <v>302</v>
@@ -4686,25 +4801,25 @@
       <c r="F6" s="19" t="s">
         <v>307</v>
       </c>
-      <c r="G6" s="34">
+      <c r="G6" s="33">
         <v>46258</v>
       </c>
-      <c r="H6" s="34">
+      <c r="H6" s="33">
         <v>46265</v>
       </c>
       <c r="I6" s="37">
         <v>25460</v>
       </c>
-      <c r="J6" s="39" t="s">
-        <v>312</v>
-      </c>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
-      <c r="M6" s="17"/>
-      <c r="N6" s="17"/>
-    </row>
-    <row r="7" spans="1:14">
-      <c r="A7" s="22" t="str">
+      <c r="J6" s="35" t="s">
+        <v>311</v>
+      </c>
+      <c r="K6" s="33">
+        <v>46307</v>
+      </c>
+      <c r="L6" s="39"/>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="41" t="str">
         <f>Exercise!B7</f>
         <v>ลำดับที่</v>
       </c>
@@ -4716,20 +4831,34 @@
         <f>Exercise!D7</f>
         <v>ชื่อ-นามสกุล</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23"/>
-      <c r="F7" s="24"/>
-      <c r="G7" s="35"/>
-      <c r="H7" s="23"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="24"/>
-      <c r="K7" s="23"/>
-      <c r="L7" s="23"/>
-      <c r="M7" s="23"/>
-      <c r="N7" s="23"/>
-    </row>
-    <row r="8" spans="1:14">
-      <c r="A8" s="9" t="str">
+      <c r="D7" s="23">
+        <v>1</v>
+      </c>
+      <c r="E7" s="23">
+        <v>1</v>
+      </c>
+      <c r="F7" s="23">
+        <v>1</v>
+      </c>
+      <c r="G7" s="34">
+        <v>1</v>
+      </c>
+      <c r="H7" s="23">
+        <v>1</v>
+      </c>
+      <c r="I7" s="38">
+        <v>1</v>
+      </c>
+      <c r="J7" s="23">
+        <v>1</v>
+      </c>
+      <c r="K7" s="23">
+        <v>1</v>
+      </c>
+      <c r="L7" s="40"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="10" t="str">
         <f>Exercise!B8</f>
         <v>1</v>
       </c>
@@ -4749,20 +4878,20 @@
         <v>1</v>
       </c>
       <c r="G8" s="10"/>
-      <c r="H8" s="9">
+      <c r="H8" s="10">
         <v>1</v>
       </c>
       <c r="I8" s="38"/>
       <c r="J8" s="10">
         <v>1</v>
       </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-    </row>
-    <row r="9" spans="1:14">
-      <c r="A9" s="9" t="str">
+      <c r="K8" s="10">
+        <v>1</v>
+      </c>
+      <c r="L8" s="10"/>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="10" t="str">
         <f>Exercise!B9</f>
         <v>2</v>
       </c>
@@ -4782,7 +4911,7 @@
       <c r="G9" s="10">
         <v>1</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="10">
         <v>1</v>
       </c>
       <c r="I9" s="38">
@@ -4791,13 +4920,13 @@
       <c r="J9" s="10">
         <v>1</v>
       </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-    </row>
-    <row r="10" spans="1:14">
-      <c r="A10" s="9" t="str">
+      <c r="K9" s="10">
+        <v>1</v>
+      </c>
+      <c r="L9" s="10"/>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="10" t="str">
         <f>Exercise!B10</f>
         <v>3</v>
       </c>
@@ -4815,20 +4944,20 @@
       </c>
       <c r="F10" s="14"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="9">
+      <c r="H10" s="10">
         <v>1</v>
       </c>
       <c r="I10" s="38"/>
       <c r="J10" s="10">
         <v>1</v>
       </c>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-    </row>
-    <row r="11" spans="1:14">
-      <c r="A11" s="9" t="str">
+      <c r="K10" s="10">
+        <v>1</v>
+      </c>
+      <c r="L10" s="10"/>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="10" t="str">
         <f>Exercise!B11</f>
         <v>4</v>
       </c>
@@ -4852,7 +4981,7 @@
       <c r="G11" s="10">
         <v>1</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="10">
         <v>1</v>
       </c>
       <c r="I11" s="38">
@@ -4861,13 +4990,13 @@
       <c r="J11" s="10">
         <v>1</v>
       </c>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-    </row>
-    <row r="12" spans="1:14">
-      <c r="A12" s="9" t="str">
+      <c r="K11" s="10">
+        <v>1</v>
+      </c>
+      <c r="L11" s="10"/>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="10" t="str">
         <f>Exercise!B12</f>
         <v>5</v>
       </c>
@@ -4891,7 +5020,7 @@
       <c r="G12" s="10">
         <v>1</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="10">
         <v>1</v>
       </c>
       <c r="I12" s="38">
@@ -4900,13 +5029,11 @@
       <c r="J12" s="10">
         <v>1</v>
       </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-    </row>
-    <row r="13" spans="1:14">
-      <c r="A13" s="9" t="str">
+      <c r="K12" s="10"/>
+      <c r="L12" s="10"/>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" s="10" t="str">
         <f>Exercise!B13</f>
         <v>6</v>
       </c>
@@ -4926,7 +5053,7 @@
       <c r="G13" s="10">
         <v>1</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="10">
         <v>1</v>
       </c>
       <c r="I13" s="38">
@@ -4935,13 +5062,11 @@
       <c r="J13" s="10">
         <v>1</v>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-    </row>
-    <row r="14" spans="1:14">
-      <c r="A14" s="9" t="str">
+      <c r="K13" s="10"/>
+      <c r="L13" s="10"/>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" s="10" t="str">
         <f>Exercise!B14</f>
         <v>7</v>
       </c>
@@ -4963,20 +5088,20 @@
       <c r="G14" s="10">
         <v>1</v>
       </c>
-      <c r="H14" s="9"/>
+      <c r="H14" s="10"/>
       <c r="I14" s="38">
         <v>1</v>
       </c>
       <c r="J14" s="10">
         <v>1</v>
       </c>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-    </row>
-    <row r="15" spans="1:14">
-      <c r="A15" s="9" t="str">
+      <c r="K14" s="10">
+        <v>1</v>
+      </c>
+      <c r="L14" s="10"/>
+    </row>
+    <row r="15" spans="1:12">
+      <c r="A15" s="10" t="str">
         <f>Exercise!B15</f>
         <v>8</v>
       </c>
@@ -5000,7 +5125,7 @@
       <c r="G15" s="10">
         <v>1</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="10">
         <v>1</v>
       </c>
       <c r="I15" s="38">
@@ -5009,13 +5134,13 @@
       <c r="J15" s="10">
         <v>1</v>
       </c>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-    </row>
-    <row r="16" spans="1:14">
-      <c r="A16" s="9" t="str">
+      <c r="K15" s="10">
+        <v>1</v>
+      </c>
+      <c r="L15" s="10"/>
+    </row>
+    <row r="16" spans="1:12">
+      <c r="A16" s="10" t="str">
         <f>Exercise!B16</f>
         <v>9</v>
       </c>
@@ -5039,7 +5164,7 @@
       <c r="G16" s="10">
         <v>1</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="10">
         <v>1</v>
       </c>
       <c r="I16" s="38">
@@ -5048,13 +5173,11 @@
       <c r="J16" s="10">
         <v>1</v>
       </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" s="9" t="str">
+      <c r="K16" s="10"/>
+      <c r="L16" s="10"/>
+    </row>
+    <row r="17" spans="1:12">
+      <c r="A17" s="10" t="str">
         <f>Exercise!B17</f>
         <v>10</v>
       </c>
@@ -5078,7 +5201,7 @@
       <c r="G17" s="10">
         <v>1</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="10">
         <v>1</v>
       </c>
       <c r="I17" s="38">
@@ -5087,13 +5210,13 @@
       <c r="J17" s="10">
         <v>1</v>
       </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" s="9" t="str">
+      <c r="K17" s="10">
+        <v>1</v>
+      </c>
+      <c r="L17" s="10"/>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" s="10" t="str">
         <f>Exercise!B18</f>
         <v>11</v>
       </c>
@@ -5115,7 +5238,7 @@
       <c r="G18" s="10">
         <v>1</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="10">
         <v>1</v>
       </c>
       <c r="I18" s="38">
@@ -5124,13 +5247,13 @@
       <c r="J18" s="10">
         <v>1</v>
       </c>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-    </row>
-    <row r="19" spans="1:14">
-      <c r="A19" s="9" t="str">
+      <c r="K18" s="10">
+        <v>1</v>
+      </c>
+      <c r="L18" s="10"/>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" s="10" t="str">
         <f>Exercise!B19</f>
         <v>12</v>
       </c>
@@ -5150,7 +5273,7 @@
       <c r="G19" s="10">
         <v>1</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="10">
         <v>1</v>
       </c>
       <c r="I19" s="38">
@@ -5159,13 +5282,11 @@
       <c r="J19" s="10">
         <v>1</v>
       </c>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" s="9" t="str">
+      <c r="K19" s="10"/>
+      <c r="L19" s="10"/>
+    </row>
+    <row r="20" spans="1:12">
+      <c r="A20" s="10" t="str">
         <f>Exercise!B20</f>
         <v>13</v>
       </c>
@@ -5185,7 +5306,7 @@
       <c r="G20" s="10">
         <v>1</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="10">
         <v>1</v>
       </c>
       <c r="I20" s="38">
@@ -5194,13 +5315,13 @@
       <c r="J20" s="10">
         <v>1</v>
       </c>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" s="9" t="str">
+      <c r="K20" s="10">
+        <v>1</v>
+      </c>
+      <c r="L20" s="10"/>
+    </row>
+    <row r="21" spans="1:12">
+      <c r="A21" s="10" t="str">
         <f>Exercise!B21</f>
         <v>14</v>
       </c>
@@ -5220,18 +5341,16 @@
       </c>
       <c r="F21" s="14"/>
       <c r="G21" s="10"/>
-      <c r="H21" s="9"/>
+      <c r="H21" s="10"/>
       <c r="I21" s="38"/>
       <c r="J21" s="10">
         <v>1</v>
       </c>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-    </row>
-    <row r="22" spans="1:14">
-      <c r="A22" s="9" t="str">
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+    </row>
+    <row r="22" spans="1:12">
+      <c r="A22" s="10" t="str">
         <f>Exercise!B22</f>
         <v>15</v>
       </c>
@@ -5255,20 +5374,20 @@
       <c r="G22" s="10">
         <v>1</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="10">
         <v>1</v>
       </c>
       <c r="I22" s="38">
         <v>1</v>
       </c>
       <c r="J22" s="10"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" s="9" t="str">
+      <c r="K22" s="10">
+        <v>1</v>
+      </c>
+      <c r="L22" s="10"/>
+    </row>
+    <row r="23" spans="1:12">
+      <c r="A23" s="10" t="str">
         <f>Exercise!B23</f>
         <v>16</v>
       </c>
@@ -5292,7 +5411,7 @@
       <c r="G23" s="10">
         <v>1</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="10">
         <v>1</v>
       </c>
       <c r="I23" s="38">
@@ -5301,13 +5420,13 @@
       <c r="J23" s="10">
         <v>1</v>
       </c>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" s="9" t="str">
+      <c r="K23" s="10">
+        <v>1</v>
+      </c>
+      <c r="L23" s="10"/>
+    </row>
+    <row r="24" spans="1:12">
+      <c r="A24" s="10" t="str">
         <f>Exercise!B24</f>
         <v>17</v>
       </c>
@@ -5331,7 +5450,7 @@
       <c r="G24" s="10">
         <v>1</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="10">
         <v>1</v>
       </c>
       <c r="I24" s="38">
@@ -5340,13 +5459,13 @@
       <c r="J24" s="10">
         <v>1</v>
       </c>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-    </row>
-    <row r="25" spans="1:14">
-      <c r="A25" s="9" t="str">
+      <c r="K24" s="10">
+        <v>1</v>
+      </c>
+      <c r="L24" s="10"/>
+    </row>
+    <row r="25" spans="1:12">
+      <c r="A25" s="10" t="str">
         <f>Exercise!B25</f>
         <v>18</v>
       </c>
@@ -5370,7 +5489,7 @@
       <c r="G25" s="10">
         <v>1</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="10">
         <v>1</v>
       </c>
       <c r="I25" s="38">
@@ -5379,13 +5498,13 @@
       <c r="J25" s="10">
         <v>1</v>
       </c>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" s="9" t="str">
+      <c r="K25" s="10">
+        <v>1</v>
+      </c>
+      <c r="L25" s="10"/>
+    </row>
+    <row r="26" spans="1:12">
+      <c r="A26" s="10" t="str">
         <f>Exercise!B26</f>
         <v>19</v>
       </c>
@@ -5409,7 +5528,7 @@
       <c r="G26" s="10">
         <v>1</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="10">
         <v>1</v>
       </c>
       <c r="I26" s="38">
@@ -5418,13 +5537,13 @@
       <c r="J26" s="10">
         <v>1</v>
       </c>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" s="9" t="str">
+      <c r="K26" s="10">
+        <v>1</v>
+      </c>
+      <c r="L26" s="10"/>
+    </row>
+    <row r="27" spans="1:12">
+      <c r="A27" s="10" t="str">
         <f>Exercise!B27</f>
         <v>20</v>
       </c>
@@ -5446,7 +5565,7 @@
       <c r="G27" s="10">
         <v>1</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="10">
         <v>1</v>
       </c>
       <c r="I27" s="38">
@@ -5455,13 +5574,13 @@
       <c r="J27" s="10">
         <v>1</v>
       </c>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-    </row>
-    <row r="28" spans="1:14">
-      <c r="A28" s="9" t="str">
+      <c r="K27" s="10">
+        <v>1</v>
+      </c>
+      <c r="L27" s="10"/>
+    </row>
+    <row r="28" spans="1:12">
+      <c r="A28" s="10" t="str">
         <f>Exercise!B28</f>
         <v>21</v>
       </c>
@@ -5483,18 +5602,18 @@
       <c r="G28" s="10">
         <v>1</v>
       </c>
-      <c r="H28" s="9"/>
+      <c r="H28" s="10"/>
       <c r="I28" s="38">
         <v>1</v>
       </c>
       <c r="J28" s="10"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" s="9" t="str">
+      <c r="K28" s="10">
+        <v>1</v>
+      </c>
+      <c r="L28" s="10"/>
+    </row>
+    <row r="29" spans="1:12">
+      <c r="A29" s="10" t="str">
         <f>Exercise!B29</f>
         <v>22</v>
       </c>
@@ -5518,7 +5637,7 @@
       <c r="G29" s="10">
         <v>1</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="10">
         <v>1</v>
       </c>
       <c r="I29" s="38">
@@ -5527,13 +5646,13 @@
       <c r="J29" s="10">
         <v>1</v>
       </c>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" s="9" t="str">
+      <c r="K29" s="10">
+        <v>1</v>
+      </c>
+      <c r="L29" s="10"/>
+    </row>
+    <row r="30" spans="1:12">
+      <c r="A30" s="10" t="str">
         <f>Exercise!B30</f>
         <v>23</v>
       </c>
@@ -5557,7 +5676,7 @@
       <c r="G30" s="10">
         <v>1</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="10">
         <v>1</v>
       </c>
       <c r="I30" s="38">
@@ -5566,13 +5685,13 @@
       <c r="J30" s="10">
         <v>1</v>
       </c>
-      <c r="K30" s="9"/>
-      <c r="L30" s="9"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-    </row>
-    <row r="31" spans="1:14">
-      <c r="A31" s="9" t="str">
+      <c r="K30" s="10">
+        <v>1</v>
+      </c>
+      <c r="L30" s="10"/>
+    </row>
+    <row r="31" spans="1:12">
+      <c r="A31" s="10" t="str">
         <f>Exercise!B31</f>
         <v>24</v>
       </c>
@@ -5588,16 +5707,14 @@
       <c r="E31" s="15"/>
       <c r="F31" s="14"/>
       <c r="G31" s="10"/>
-      <c r="H31" s="9"/>
+      <c r="H31" s="10"/>
       <c r="I31" s="38"/>
       <c r="J31" s="10"/>
-      <c r="K31" s="9"/>
-      <c r="L31" s="9"/>
-      <c r="M31" s="9"/>
-      <c r="N31" s="9"/>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" s="9" t="str">
+      <c r="K31" s="10"/>
+      <c r="L31" s="10"/>
+    </row>
+    <row r="32" spans="1:12">
+      <c r="A32" s="10" t="str">
         <f>Exercise!B32</f>
         <v>25</v>
       </c>
@@ -5621,7 +5738,7 @@
       <c r="G32" s="10">
         <v>1</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="10">
         <v>1</v>
       </c>
       <c r="I32" s="38">
@@ -5630,13 +5747,13 @@
       <c r="J32" s="10">
         <v>1</v>
       </c>
-      <c r="K32" s="9"/>
-      <c r="L32" s="9"/>
-      <c r="M32" s="9"/>
-      <c r="N32" s="9"/>
-    </row>
-    <row r="33" spans="1:14">
-      <c r="A33" s="9" t="str">
+      <c r="K32" s="10">
+        <v>1</v>
+      </c>
+      <c r="L32" s="10"/>
+    </row>
+    <row r="33" spans="1:12">
+      <c r="A33" s="10" t="str">
         <f>Exercise!B33</f>
         <v>26</v>
       </c>
@@ -5658,7 +5775,7 @@
       <c r="G33" s="10">
         <v>1</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="10">
         <v>1</v>
       </c>
       <c r="I33" s="38">
@@ -5667,13 +5784,13 @@
       <c r="J33" s="10">
         <v>1</v>
       </c>
-      <c r="K33" s="9"/>
-      <c r="L33" s="9"/>
-      <c r="M33" s="9"/>
-      <c r="N33" s="9"/>
-    </row>
-    <row r="34" spans="1:14">
-      <c r="A34" s="9" t="str">
+      <c r="K33" s="10">
+        <v>1</v>
+      </c>
+      <c r="L33" s="10"/>
+    </row>
+    <row r="34" spans="1:12">
+      <c r="A34" s="10" t="str">
         <f>Exercise!B34</f>
         <v>27</v>
       </c>
@@ -5697,7 +5814,7 @@
       <c r="G34" s="10">
         <v>1</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="10">
         <v>1</v>
       </c>
       <c r="I34" s="38">
@@ -5706,13 +5823,13 @@
       <c r="J34" s="10">
         <v>1</v>
       </c>
-      <c r="K34" s="9"/>
-      <c r="L34" s="9"/>
-      <c r="M34" s="9"/>
-      <c r="N34" s="9"/>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" s="9" t="str">
+      <c r="K34" s="10">
+        <v>1</v>
+      </c>
+      <c r="L34" s="10"/>
+    </row>
+    <row r="35" spans="1:12">
+      <c r="A35" s="10" t="str">
         <f>Exercise!B35</f>
         <v>28</v>
       </c>
@@ -5736,7 +5853,7 @@
       <c r="G35" s="10">
         <v>1</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="10">
         <v>1</v>
       </c>
       <c r="I35" s="38">
@@ -5745,13 +5862,13 @@
       <c r="J35" s="10">
         <v>1</v>
       </c>
-      <c r="K35" s="9"/>
-      <c r="L35" s="9"/>
-      <c r="M35" s="9"/>
-      <c r="N35" s="9"/>
-    </row>
-    <row r="36" spans="1:14">
-      <c r="A36" s="9" t="str">
+      <c r="K35" s="10">
+        <v>1</v>
+      </c>
+      <c r="L35" s="10"/>
+    </row>
+    <row r="36" spans="1:12">
+      <c r="A36" s="10" t="str">
         <f>Exercise!B36</f>
         <v>29</v>
       </c>
@@ -5775,20 +5892,20 @@
       <c r="G36" s="10">
         <v>1</v>
       </c>
-      <c r="H36" s="9"/>
+      <c r="H36" s="10"/>
       <c r="I36" s="38">
         <v>1</v>
       </c>
       <c r="J36" s="10">
         <v>1</v>
       </c>
-      <c r="K36" s="9"/>
-      <c r="L36" s="9"/>
-      <c r="M36" s="9"/>
-      <c r="N36" s="9"/>
-    </row>
-    <row r="37" spans="1:14">
-      <c r="A37" s="9" t="str">
+      <c r="K36" s="10">
+        <v>1</v>
+      </c>
+      <c r="L36" s="10"/>
+    </row>
+    <row r="37" spans="1:12">
+      <c r="A37" s="10" t="str">
         <f>Exercise!B37</f>
         <v>30</v>
       </c>
@@ -5812,7 +5929,7 @@
       <c r="G37" s="10">
         <v>1</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="10">
         <v>1</v>
       </c>
       <c r="I37" s="38">
@@ -5821,13 +5938,13 @@
       <c r="J37" s="10">
         <v>1</v>
       </c>
-      <c r="K37" s="9"/>
-      <c r="L37" s="9"/>
-      <c r="M37" s="9"/>
-      <c r="N37" s="9"/>
-    </row>
-    <row r="38" spans="1:14">
-      <c r="A38" s="9" t="str">
+      <c r="K37" s="10">
+        <v>1</v>
+      </c>
+      <c r="L37" s="10"/>
+    </row>
+    <row r="38" spans="1:12">
+      <c r="A38" s="10" t="str">
         <f>Exercise!B38</f>
         <v>31</v>
       </c>
@@ -5849,7 +5966,7 @@
       <c r="G38" s="10">
         <v>1</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="10">
         <v>1</v>
       </c>
       <c r="I38" s="38">
@@ -5858,13 +5975,13 @@
       <c r="J38" s="10">
         <v>1</v>
       </c>
-      <c r="K38" s="9"/>
-      <c r="L38" s="9"/>
-      <c r="M38" s="9"/>
-      <c r="N38" s="9"/>
-    </row>
-    <row r="39" spans="1:14">
-      <c r="A39" s="9" t="str">
+      <c r="K38" s="10">
+        <v>1</v>
+      </c>
+      <c r="L38" s="10"/>
+    </row>
+    <row r="39" spans="1:12">
+      <c r="A39" s="10" t="str">
         <f>Exercise!B39</f>
         <v>32</v>
       </c>
@@ -5888,7 +6005,7 @@
       <c r="G39" s="10">
         <v>1</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="10">
         <v>1</v>
       </c>
       <c r="I39" s="38">
@@ -5897,13 +6014,13 @@
       <c r="J39" s="10">
         <v>1</v>
       </c>
-      <c r="K39" s="9"/>
-      <c r="L39" s="9"/>
-      <c r="M39" s="9"/>
-      <c r="N39" s="9"/>
-    </row>
-    <row r="40" spans="1:14">
-      <c r="A40" s="9" t="str">
+      <c r="K39" s="10">
+        <v>1</v>
+      </c>
+      <c r="L39" s="10"/>
+    </row>
+    <row r="40" spans="1:12">
+      <c r="A40" s="10" t="str">
         <f>Exercise!B40</f>
         <v>33</v>
       </c>
@@ -5927,20 +6044,20 @@
       <c r="G40" s="10">
         <v>1</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="10">
         <v>1</v>
       </c>
       <c r="I40" s="38">
         <v>1</v>
       </c>
       <c r="J40" s="10"/>
-      <c r="K40" s="9"/>
-      <c r="L40" s="9"/>
-      <c r="M40" s="9"/>
-      <c r="N40" s="9"/>
-    </row>
-    <row r="41" spans="1:14">
-      <c r="A41" s="9" t="str">
+      <c r="K40" s="10">
+        <v>1</v>
+      </c>
+      <c r="L40" s="10"/>
+    </row>
+    <row r="41" spans="1:12">
+      <c r="A41" s="10" t="str">
         <f>Exercise!B41</f>
         <v>34</v>
       </c>
@@ -5964,7 +6081,7 @@
       <c r="G41" s="10">
         <v>1</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="10">
         <v>1</v>
       </c>
       <c r="I41" s="38">
@@ -5973,13 +6090,13 @@
       <c r="J41" s="10">
         <v>1</v>
       </c>
-      <c r="K41" s="9"/>
-      <c r="L41" s="9"/>
-      <c r="M41" s="9"/>
-      <c r="N41" s="9"/>
-    </row>
-    <row r="42" spans="1:14">
-      <c r="A42" s="9" t="str">
+      <c r="K41" s="10">
+        <v>1</v>
+      </c>
+      <c r="L41" s="10"/>
+    </row>
+    <row r="42" spans="1:12">
+      <c r="A42" s="10" t="str">
         <f>Exercise!B42</f>
         <v>35</v>
       </c>
@@ -6003,7 +6120,7 @@
       <c r="G42" s="10">
         <v>1</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="10">
         <v>1</v>
       </c>
       <c r="I42" s="38">
@@ -6012,13 +6129,13 @@
       <c r="J42" s="10">
         <v>1</v>
       </c>
-      <c r="K42" s="9"/>
-      <c r="L42" s="9"/>
-      <c r="M42" s="9"/>
-      <c r="N42" s="9"/>
-    </row>
-    <row r="43" spans="1:14">
-      <c r="A43" s="9" t="str">
+      <c r="K42" s="10">
+        <v>1</v>
+      </c>
+      <c r="L42" s="10"/>
+    </row>
+    <row r="43" spans="1:12">
+      <c r="A43" s="10" t="str">
         <f>Exercise!B43</f>
         <v>36</v>
       </c>
@@ -6042,7 +6159,7 @@
       <c r="G43" s="10">
         <v>1</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="10">
         <v>1</v>
       </c>
       <c r="I43" s="38">
@@ -6051,13 +6168,13 @@
       <c r="J43" s="10">
         <v>1</v>
       </c>
-      <c r="K43" s="9"/>
-      <c r="L43" s="9"/>
-      <c r="M43" s="9"/>
-      <c r="N43" s="9"/>
-    </row>
-    <row r="44" spans="1:14">
-      <c r="A44" s="9" t="str">
+      <c r="K43" s="10">
+        <v>1</v>
+      </c>
+      <c r="L43" s="10"/>
+    </row>
+    <row r="44" spans="1:12">
+      <c r="A44" s="10" t="str">
         <f>Exercise!B44</f>
         <v>37</v>
       </c>
@@ -6081,7 +6198,7 @@
       <c r="G44" s="10">
         <v>1</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="10">
         <v>1</v>
       </c>
       <c r="I44" s="38">
@@ -6090,13 +6207,13 @@
       <c r="J44" s="10">
         <v>1</v>
       </c>
-      <c r="K44" s="9"/>
-      <c r="L44" s="9"/>
-      <c r="M44" s="9"/>
-      <c r="N44" s="9"/>
-    </row>
-    <row r="45" spans="1:14">
-      <c r="A45" s="9" t="str">
+      <c r="K44" s="10">
+        <v>1</v>
+      </c>
+      <c r="L44" s="10"/>
+    </row>
+    <row r="45" spans="1:12">
+      <c r="A45" s="10" t="str">
         <f>Exercise!B45</f>
         <v>38</v>
       </c>
@@ -6120,7 +6237,7 @@
       <c r="G45" s="10">
         <v>1</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="10">
         <v>1</v>
       </c>
       <c r="I45" s="38">
@@ -6129,13 +6246,13 @@
       <c r="J45" s="10">
         <v>1</v>
       </c>
-      <c r="K45" s="9"/>
-      <c r="L45" s="9"/>
-      <c r="M45" s="9"/>
-      <c r="N45" s="9"/>
-    </row>
-    <row r="46" spans="1:14">
-      <c r="A46" s="9" t="str">
+      <c r="K45" s="10">
+        <v>1</v>
+      </c>
+      <c r="L45" s="10"/>
+    </row>
+    <row r="46" spans="1:12">
+      <c r="A46" s="10" t="str">
         <f>Exercise!B46</f>
         <v>39</v>
       </c>
@@ -6159,7 +6276,7 @@
       <c r="G46" s="10">
         <v>1</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="10">
         <v>1</v>
       </c>
       <c r="I46" s="38">
@@ -6168,13 +6285,13 @@
       <c r="J46" s="10">
         <v>1</v>
       </c>
-      <c r="K46" s="9"/>
-      <c r="L46" s="9"/>
-      <c r="M46" s="9"/>
-      <c r="N46" s="9"/>
-    </row>
-    <row r="47" spans="1:14">
-      <c r="A47" s="9" t="str">
+      <c r="K46" s="10">
+        <v>1</v>
+      </c>
+      <c r="L46" s="10"/>
+    </row>
+    <row r="47" spans="1:12">
+      <c r="A47" s="10" t="str">
         <f>Exercise!B47</f>
         <v>40</v>
       </c>
@@ -6198,7 +6315,7 @@
       <c r="G47" s="10">
         <v>1</v>
       </c>
-      <c r="H47" s="9">
+      <c r="H47" s="10">
         <v>1</v>
       </c>
       <c r="I47" s="38">
@@ -6207,13 +6324,11 @@
       <c r="J47" s="10">
         <v>1</v>
       </c>
-      <c r="K47" s="9"/>
-      <c r="L47" s="9"/>
-      <c r="M47" s="9"/>
-      <c r="N47" s="9"/>
-    </row>
-    <row r="48" spans="1:14">
-      <c r="A48" s="9" t="str">
+      <c r="K47" s="10"/>
+      <c r="L47" s="10"/>
+    </row>
+    <row r="48" spans="1:12">
+      <c r="A48" s="10" t="str">
         <f>Exercise!B48</f>
         <v>41</v>
       </c>
@@ -6237,7 +6352,7 @@
       <c r="G48" s="10">
         <v>1</v>
       </c>
-      <c r="H48" s="9">
+      <c r="H48" s="10">
         <v>1</v>
       </c>
       <c r="I48" s="38">
@@ -6246,13 +6361,13 @@
       <c r="J48" s="10">
         <v>1</v>
       </c>
-      <c r="K48" s="9"/>
-      <c r="L48" s="9"/>
-      <c r="M48" s="9"/>
-      <c r="N48" s="9"/>
-    </row>
-    <row r="49" spans="1:14">
-      <c r="A49" s="9" t="str">
+      <c r="K48" s="10">
+        <v>1</v>
+      </c>
+      <c r="L48" s="10"/>
+    </row>
+    <row r="49" spans="1:12">
+      <c r="A49" s="10" t="str">
         <f>Exercise!B49</f>
         <v>42</v>
       </c>
@@ -6276,7 +6391,7 @@
       <c r="G49" s="10">
         <v>1</v>
       </c>
-      <c r="H49" s="9">
+      <c r="H49" s="10">
         <v>1</v>
       </c>
       <c r="I49" s="38">
@@ -6285,13 +6400,13 @@
       <c r="J49" s="10">
         <v>1</v>
       </c>
-      <c r="K49" s="9"/>
-      <c r="L49" s="9"/>
-      <c r="M49" s="9"/>
-      <c r="N49" s="9"/>
-    </row>
-    <row r="50" spans="1:14">
-      <c r="A50" s="9" t="str">
+      <c r="K49" s="10">
+        <v>1</v>
+      </c>
+      <c r="L49" s="10"/>
+    </row>
+    <row r="50" spans="1:12">
+      <c r="A50" s="10" t="str">
         <f>Exercise!B50</f>
         <v>43</v>
       </c>
@@ -6315,7 +6430,7 @@
       <c r="G50" s="10">
         <v>1</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H50" s="10">
         <v>1</v>
       </c>
       <c r="I50" s="38">
@@ -6324,13 +6439,13 @@
       <c r="J50" s="10">
         <v>1</v>
       </c>
-      <c r="K50" s="9"/>
-      <c r="L50" s="9"/>
-      <c r="M50" s="9"/>
-      <c r="N50" s="9"/>
-    </row>
-    <row r="51" spans="1:14">
-      <c r="A51" s="9" t="str">
+      <c r="K50" s="10">
+        <v>1</v>
+      </c>
+      <c r="L50" s="10"/>
+    </row>
+    <row r="51" spans="1:12">
+      <c r="A51" s="10" t="str">
         <f>Exercise!B51</f>
         <v>44</v>
       </c>
@@ -6354,7 +6469,7 @@
       <c r="G51" s="10">
         <v>1</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H51" s="10">
         <v>1</v>
       </c>
       <c r="I51" s="38">
@@ -6363,13 +6478,13 @@
       <c r="J51" s="10">
         <v>1</v>
       </c>
-      <c r="K51" s="9"/>
-      <c r="L51" s="9"/>
-      <c r="M51" s="9"/>
-      <c r="N51" s="9"/>
-    </row>
-    <row r="52" spans="1:14">
-      <c r="A52" s="9" t="str">
+      <c r="K51" s="10">
+        <v>1</v>
+      </c>
+      <c r="L51" s="10"/>
+    </row>
+    <row r="52" spans="1:12">
+      <c r="A52" s="10" t="str">
         <f>Exercise!B52</f>
         <v>45</v>
       </c>
@@ -6393,7 +6508,7 @@
       <c r="G52" s="10">
         <v>1</v>
       </c>
-      <c r="H52" s="9">
+      <c r="H52" s="10">
         <v>1</v>
       </c>
       <c r="I52" s="38">
@@ -6402,13 +6517,13 @@
       <c r="J52" s="10">
         <v>1</v>
       </c>
-      <c r="K52" s="9"/>
-      <c r="L52" s="9"/>
-      <c r="M52" s="9"/>
-      <c r="N52" s="9"/>
-    </row>
-    <row r="53" spans="1:14">
-      <c r="A53" s="9" t="str">
+      <c r="K52" s="10">
+        <v>1</v>
+      </c>
+      <c r="L52" s="10"/>
+    </row>
+    <row r="53" spans="1:12">
+      <c r="A53" s="10" t="str">
         <f>Exercise!B53</f>
         <v>46</v>
       </c>
@@ -6432,7 +6547,7 @@
       <c r="G53" s="10">
         <v>1</v>
       </c>
-      <c r="H53" s="9">
+      <c r="H53" s="10">
         <v>1</v>
       </c>
       <c r="I53" s="38">
@@ -6441,10 +6556,10 @@
       <c r="J53" s="10">
         <v>1</v>
       </c>
-      <c r="K53" s="9"/>
-      <c r="L53" s="9"/>
-      <c r="M53" s="9"/>
-      <c r="N53" s="9"/>
+      <c r="K53" s="10">
+        <v>1</v>
+      </c>
+      <c r="L53" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
